--- a/data/Classes_2026_biology.xlsx
+++ b/data/Classes_2026_biology.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9264"/>
+    <workbookView windowWidth="22188" windowHeight="8724"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="375">
   <si>
     <t>Family</t>
   </si>
@@ -233,7 +233,7 @@
     <t>Анар</t>
   </si>
   <si>
-    <t>Садиг оглы</t>
+    <t>Садигоглы</t>
   </si>
   <si>
     <t>st139799</t>
@@ -1146,6 +1146,15 @@
   </si>
   <si>
     <t>st160537</t>
+  </si>
+  <si>
+    <t>Половко</t>
+  </si>
+  <si>
+    <t>Вячеславович</t>
+  </si>
+  <si>
+    <t>st160533</t>
   </si>
 </sst>
 </file>
@@ -2303,7 +2312,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.5555555555556" style="1" customWidth="1"/>
@@ -4039,7 +4048,6 @@
       <c r="B124" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="1"/>
       <c r="D124" s="3" t="s">
         <v>357</v>
       </c>
@@ -4112,6 +4120,20 @@
       </c>
       <c r="D129" s="3" t="s">
         <v>371</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:4">
+      <c r="A130" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/data/Classes_2026_biology.xlsx
+++ b/data/Classes_2026_biology.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8724"/>
+    <workbookView windowWidth="22188" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$2:$D$129</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="505">
   <si>
     <t>Family</t>
   </si>
@@ -1155,6 +1156,396 @@
   </si>
   <si>
     <t>st160533</t>
+  </si>
+  <si>
+    <t>ФИО</t>
+  </si>
+  <si>
+    <t>Александрова Анна</t>
+  </si>
+  <si>
+    <t>Афонина Злата</t>
+  </si>
+  <si>
+    <t>Беленина Кристина</t>
+  </si>
+  <si>
+    <t>Бутикова Вероника</t>
+  </si>
+  <si>
+    <t>Гладских Виктория</t>
+  </si>
+  <si>
+    <t>Головко Анна</t>
+  </si>
+  <si>
+    <t>Кокотеева Софья</t>
+  </si>
+  <si>
+    <t>Колесниченко Софья</t>
+  </si>
+  <si>
+    <t>Коротовских Маргарита</t>
+  </si>
+  <si>
+    <t>Кравчук Юлия</t>
+  </si>
+  <si>
+    <t>Курочкина Юлиана</t>
+  </si>
+  <si>
+    <t>Лукина София</t>
+  </si>
+  <si>
+    <t>Лысненко Александра</t>
+  </si>
+  <si>
+    <t>Морозова Дарья</t>
+  </si>
+  <si>
+    <t>Погонина Софья</t>
+  </si>
+  <si>
+    <t>Сучков Руслан</t>
+  </si>
+  <si>
+    <t>Третнова Виктория</t>
+  </si>
+  <si>
+    <t>Фельзингер Анастасия</t>
+  </si>
+  <si>
+    <t>Алексеев Павел</t>
+  </si>
+  <si>
+    <t>Ахатова Яна</t>
+  </si>
+  <si>
+    <t>Вербицкий Эльмир</t>
+  </si>
+  <si>
+    <t>Виноградов Кирилл</t>
+  </si>
+  <si>
+    <t>Волкова Софья</t>
+  </si>
+  <si>
+    <t>Груздева Ольга</t>
+  </si>
+  <si>
+    <t>Кисель Полина</t>
+  </si>
+  <si>
+    <t>Коваль Яна</t>
+  </si>
+  <si>
+    <t>Комарова Ксения</t>
+  </si>
+  <si>
+    <t>Кононова Варвара</t>
+  </si>
+  <si>
+    <t>Королев Илья</t>
+  </si>
+  <si>
+    <t>Король Ника</t>
+  </si>
+  <si>
+    <t>Кузина Вероника</t>
+  </si>
+  <si>
+    <t>Кузьмина Анастасия</t>
+  </si>
+  <si>
+    <t>Курганская Вера</t>
+  </si>
+  <si>
+    <t>Лебедева Галина</t>
+  </si>
+  <si>
+    <t>Соболева Дарья</t>
+  </si>
+  <si>
+    <t>Шилко София</t>
+  </si>
+  <si>
+    <t>Гайворонская Милослава</t>
+  </si>
+  <si>
+    <t>Данилова Анастасия</t>
+  </si>
+  <si>
+    <t>Данюк Дарья</t>
+  </si>
+  <si>
+    <t>Елисеева Варвара</t>
+  </si>
+  <si>
+    <t>Ермолаева Дарья</t>
+  </si>
+  <si>
+    <t>Ерохина Алиса</t>
+  </si>
+  <si>
+    <t>Жданова Дарья</t>
+  </si>
+  <si>
+    <t>Захаричева Екатерина</t>
+  </si>
+  <si>
+    <t>Зонова Анна</t>
+  </si>
+  <si>
+    <t>Лагутина Полина</t>
+  </si>
+  <si>
+    <t>Нугманова Эллина</t>
+  </si>
+  <si>
+    <t>Попова Диана</t>
+  </si>
+  <si>
+    <t>Редькина Алена</t>
+  </si>
+  <si>
+    <t>Салахян Иван</t>
+  </si>
+  <si>
+    <t>Фисенко Владислав</t>
+  </si>
+  <si>
+    <t>Чорду Василий</t>
+  </si>
+  <si>
+    <t>Чуксина Яна</t>
+  </si>
+  <si>
+    <t>Шпанькова Алёна</t>
+  </si>
+  <si>
+    <t>Алямская Ксения</t>
+  </si>
+  <si>
+    <t>Капитонова Ксения</t>
+  </si>
+  <si>
+    <t>Капралова Мария</t>
+  </si>
+  <si>
+    <t>Келембет Николай</t>
+  </si>
+  <si>
+    <t>Левина Елизавета</t>
+  </si>
+  <si>
+    <t>Лопатина Александра Мафра</t>
+  </si>
+  <si>
+    <t>Манич Мария</t>
+  </si>
+  <si>
+    <t>Михеева Ярослава</t>
+  </si>
+  <si>
+    <t>Некрасова Ольга</t>
+  </si>
+  <si>
+    <t>Нефёдова Ульяна</t>
+  </si>
+  <si>
+    <t>Окунева Вера</t>
+  </si>
+  <si>
+    <t>Охримчук Анастасия</t>
+  </si>
+  <si>
+    <t>Панков Роман</t>
+  </si>
+  <si>
+    <t>Половко Артём</t>
+  </si>
+  <si>
+    <t>Попова Арина</t>
+  </si>
+  <si>
+    <t>Прядкин Даниил</t>
+  </si>
+  <si>
+    <t>Риверфорт Адель</t>
+  </si>
+  <si>
+    <t>Сидоров Игорь</t>
+  </si>
+  <si>
+    <t>Тебенькова Елизавета</t>
+  </si>
+  <si>
+    <t>Бойкова Полина</t>
+  </si>
+  <si>
+    <t>Вайман Марианна</t>
+  </si>
+  <si>
+    <t>Зайцева София</t>
+  </si>
+  <si>
+    <t>Иванищенко Игорь</t>
+  </si>
+  <si>
+    <t>Корнилов Борис</t>
+  </si>
+  <si>
+    <t>Коробкин Никита</t>
+  </si>
+  <si>
+    <t>Лебедева Екатерина</t>
+  </si>
+  <si>
+    <t>Наговицына Кристина</t>
+  </si>
+  <si>
+    <t>Савина Анастасия</t>
+  </si>
+  <si>
+    <t>Смирнова Дарья</t>
+  </si>
+  <si>
+    <t>Тихомирова Анна</t>
+  </si>
+  <si>
+    <t>Тулакина Рената</t>
+  </si>
+  <si>
+    <t>Тяглова Анна Олеговна</t>
+  </si>
+  <si>
+    <t>Фаддеев Илья</t>
+  </si>
+  <si>
+    <t>Шевченко Наталья</t>
+  </si>
+  <si>
+    <t>Шитикова Елизавета</t>
+  </si>
+  <si>
+    <t>Шушакова Мария</t>
+  </si>
+  <si>
+    <t>Щеклеина Елизавета</t>
+  </si>
+  <si>
+    <t>Юганова Полина</t>
+  </si>
+  <si>
+    <t>Аллахвердиев Анар</t>
+  </si>
+  <si>
+    <t>Алябьев Артур</t>
+  </si>
+  <si>
+    <t>Байко Дмитрий</t>
+  </si>
+  <si>
+    <t>Батуро Мария</t>
+  </si>
+  <si>
+    <t>Белова Виктория</t>
+  </si>
+  <si>
+    <t>Велькина Виктория</t>
+  </si>
+  <si>
+    <t>Винтер Алиса</t>
+  </si>
+  <si>
+    <t>Габдульбарова Алина</t>
+  </si>
+  <si>
+    <t>Иванова Арина</t>
+  </si>
+  <si>
+    <t>Иванова Вероника</t>
+  </si>
+  <si>
+    <t>Каштанов Андрей</t>
+  </si>
+  <si>
+    <t>Коровина Полина</t>
+  </si>
+  <si>
+    <t>Мелихова Лилия</t>
+  </si>
+  <si>
+    <t>Назаров Тимур</t>
+  </si>
+  <si>
+    <t>Петров Артем</t>
+  </si>
+  <si>
+    <t>Рыжова Ирина</t>
+  </si>
+  <si>
+    <t>Таропчина Виктория</t>
+  </si>
+  <si>
+    <t>Ушаков Никита</t>
+  </si>
+  <si>
+    <t>Фрайтаг Хенрик Николай</t>
+  </si>
+  <si>
+    <t>Акмалов Артур</t>
+  </si>
+  <si>
+    <t>Глазова Юлия</t>
+  </si>
+  <si>
+    <t>Гомонова Анжелика</t>
+  </si>
+  <si>
+    <t>Давыдов Дмитрий</t>
+  </si>
+  <si>
+    <t>Ершова Татьяна</t>
+  </si>
+  <si>
+    <t>Ефименко Екатерина</t>
+  </si>
+  <si>
+    <t>Константинов Иван</t>
+  </si>
+  <si>
+    <t>Криштопов Никита</t>
+  </si>
+  <si>
+    <t>Петровский Максим</t>
+  </si>
+  <si>
+    <t>Погорелова Полина</t>
+  </si>
+  <si>
+    <t>Проскурня Валерия</t>
+  </si>
+  <si>
+    <t>Савчук Андрей</t>
+  </si>
+  <si>
+    <t>Свистун Никита</t>
+  </si>
+  <si>
+    <t>Соколов Виктор</t>
+  </si>
+  <si>
+    <t>Татаркова Полина</t>
+  </si>
+  <si>
+    <t>Фау Артем</t>
+  </si>
+  <si>
+    <t>Хяннинен Тимофей</t>
+  </si>
+  <si>
+    <t>Янкова Анастасия</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1558,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1176,10 +1567,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1195,13 +1588,19 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF262626"/>
+      <color rgb="FF222222"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF222222"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF262626"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -1357,12 +1756,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1372,14 +1777,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFF4CCCC"/>
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1569,12 +1974,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1678,31 +2113,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1711,37 +2143,37 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1756,87 +2188,102 @@
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2315,24 +2762,24 @@
   <dimension ref="A1:D130"/>
   <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.5555555555556" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6296296296296" style="1"/>
-    <col min="3" max="3" width="16.2222222222222" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="12.6296296296296" style="1"/>
+    <col min="1" max="1" width="15.5555555555556" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.6296296296296" style="7"/>
+    <col min="3" max="3" width="16.2222222222222" style="7" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="12.6296296296296" style="7"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2340,10 +2787,10 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2354,10 +2801,10 @@
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2368,10 +2815,10 @@
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -2382,10 +2829,10 @@
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2396,10 +2843,10 @@
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2410,10 +2857,10 @@
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2424,10 +2871,10 @@
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2438,10 +2885,10 @@
       <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2452,10 +2899,10 @@
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2466,10 +2913,10 @@
       <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2480,10 +2927,10 @@
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -2494,10 +2941,10 @@
       <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2508,10 +2955,10 @@
       <c r="A14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2522,13 +2969,13 @@
       <c r="A15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="9" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2536,10 +2983,10 @@
       <c r="A16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2550,10 +2997,10 @@
       <c r="A17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="7" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -2564,10 +3011,10 @@
       <c r="A18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="7" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2578,10 +3025,10 @@
       <c r="A19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="7" t="s">
         <v>67</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -2592,10 +3039,10 @@
       <c r="A20" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2606,10 +3053,10 @@
       <c r="A21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="7" t="s">
         <v>73</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2620,10 +3067,10 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2634,10 +3081,10 @@
       <c r="A23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -2648,10 +3095,10 @@
       <c r="A24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -2662,10 +3109,10 @@
       <c r="A25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -2676,10 +3123,10 @@
       <c r="A26" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -2690,10 +3137,10 @@
       <c r="A27" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="7" t="s">
         <v>91</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -2704,10 +3151,10 @@
       <c r="A28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -2718,10 +3165,10 @@
       <c r="A29" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="7" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -2732,10 +3179,10 @@
       <c r="A30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="7" t="s">
         <v>102</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -2746,10 +3193,10 @@
       <c r="A31" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -2760,10 +3207,10 @@
       <c r="A32" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="7" t="s">
         <v>107</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -2774,10 +3221,10 @@
       <c r="A33" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -2788,10 +3235,10 @@
       <c r="A34" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2802,10 +3249,10 @@
       <c r="A35" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="7" t="s">
         <v>118</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -2816,10 +3263,10 @@
       <c r="A36" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -2830,10 +3277,10 @@
       <c r="A37" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="7" t="s">
         <v>98</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -2844,10 +3291,10 @@
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="7" t="s">
         <v>126</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -2858,10 +3305,10 @@
       <c r="A39" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="7" t="s">
         <v>102</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -2872,10 +3319,10 @@
       <c r="A40" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -2886,10 +3333,10 @@
       <c r="A41" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -2900,10 +3347,10 @@
       <c r="A42" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="7" t="s">
         <v>63</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -2914,10 +3361,10 @@
       <c r="A43" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -2928,10 +3375,10 @@
       <c r="A44" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -2939,16 +3386,16 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:4">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2956,10 +3403,10 @@
       <c r="A46" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -2970,10 +3417,10 @@
       <c r="A47" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="7" t="s">
         <v>149</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -2984,10 +3431,10 @@
       <c r="A48" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -2998,10 +3445,10 @@
       <c r="A49" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -3012,10 +3459,10 @@
       <c r="A50" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="7" t="s">
         <v>159</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -3026,10 +3473,10 @@
       <c r="A51" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -3040,10 +3487,10 @@
       <c r="A52" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="7" t="s">
         <v>166</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -3054,10 +3501,10 @@
       <c r="A53" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="7" t="s">
         <v>170</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -3068,10 +3515,10 @@
       <c r="A54" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="7" t="s">
         <v>102</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -3082,10 +3529,10 @@
       <c r="A55" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -3096,10 +3543,10 @@
       <c r="A56" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -3110,10 +3557,10 @@
       <c r="A57" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="7" t="s">
         <v>180</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -3124,10 +3571,10 @@
       <c r="A58" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -3138,10 +3585,10 @@
       <c r="A59" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -3152,10 +3599,10 @@
       <c r="A60" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -3166,10 +3613,10 @@
       <c r="A61" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="7" t="s">
         <v>191</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -3180,10 +3627,10 @@
       <c r="A62" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -3194,10 +3641,10 @@
       <c r="A63" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="7" t="s">
         <v>198</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -3208,10 +3655,10 @@
       <c r="A64" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="7" t="s">
         <v>201</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -3222,10 +3669,10 @@
       <c r="A65" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -3236,10 +3683,10 @@
       <c r="A66" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -3250,13 +3697,13 @@
       <c r="A67" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="6" t="s">
         <v>211</v>
       </c>
     </row>
@@ -3264,10 +3711,10 @@
       <c r="A68" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -3278,10 +3725,10 @@
       <c r="A69" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="7" t="s">
         <v>217</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -3292,10 +3739,10 @@
       <c r="A70" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="7" t="s">
         <v>191</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -3306,10 +3753,10 @@
       <c r="A71" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -3320,10 +3767,10 @@
       <c r="A72" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="7" t="s">
         <v>217</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -3334,10 +3781,10 @@
       <c r="A73" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -3348,10 +3795,10 @@
       <c r="A74" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="7" t="s">
         <v>230</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -3362,10 +3809,10 @@
       <c r="A75" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -3376,10 +3823,10 @@
       <c r="A76" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="7" t="s">
         <v>230</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -3390,10 +3837,10 @@
       <c r="A77" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="7" t="s">
         <v>149</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -3404,10 +3851,10 @@
       <c r="A78" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="7" t="s">
         <v>240</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -3418,10 +3865,10 @@
       <c r="A79" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="7" t="s">
         <v>243</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -3432,10 +3879,10 @@
       <c r="A80" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -3446,10 +3893,10 @@
       <c r="A81" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -3460,10 +3907,10 @@
       <c r="A82" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D82" s="3" t="s">
@@ -3474,10 +3921,10 @@
       <c r="A83" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="7" t="s">
         <v>217</v>
       </c>
       <c r="D83" s="3" t="s">
@@ -3488,10 +3935,10 @@
       <c r="A84" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -3502,10 +3949,10 @@
       <c r="A85" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="7" t="s">
         <v>217</v>
       </c>
       <c r="D85" s="3" t="s">
@@ -3516,10 +3963,10 @@
       <c r="A86" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D86" s="3" t="s">
@@ -3530,13 +3977,13 @@
       <c r="A87" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="5" t="s">
         <v>264</v>
       </c>
     </row>
@@ -3544,10 +3991,10 @@
       <c r="A88" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="7" t="s">
         <v>266</v>
       </c>
       <c r="D88" s="3" t="s">
@@ -3558,10 +4005,10 @@
       <c r="A89" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="7" t="s">
         <v>270</v>
       </c>
       <c r="D89" s="3" t="s">
@@ -3572,10 +4019,10 @@
       <c r="A90" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="7" t="s">
         <v>273</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -3586,10 +4033,10 @@
       <c r="A91" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="7" t="s">
         <v>276</v>
       </c>
       <c r="D91" s="3" t="s">
@@ -3600,10 +4047,10 @@
       <c r="A92" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D92" s="3" t="s">
@@ -3614,10 +4061,10 @@
       <c r="A93" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="7" t="s">
         <v>191</v>
       </c>
       <c r="D93" s="3" t="s">
@@ -3628,10 +4075,10 @@
       <c r="A94" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D94" s="3" t="s">
@@ -3642,10 +4089,10 @@
       <c r="A95" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D95" s="3" t="s">
@@ -3656,10 +4103,10 @@
       <c r="A96" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D96" s="3" t="s">
@@ -3670,10 +4117,10 @@
       <c r="A97" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D97" s="3" t="s">
@@ -3684,10 +4131,10 @@
       <c r="A98" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D98" s="3" t="s">
@@ -3698,13 +4145,13 @@
       <c r="A99" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D99" s="5" t="s">
+      <c r="D99" s="9" t="s">
         <v>296</v>
       </c>
     </row>
@@ -3712,10 +4159,10 @@
       <c r="A100" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="7" t="s">
         <v>299</v>
       </c>
       <c r="D100" s="3" t="s">
@@ -3726,10 +4173,10 @@
       <c r="A101" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="7" t="s">
         <v>243</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -3740,10 +4187,10 @@
       <c r="A102" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="7" t="s">
         <v>243</v>
       </c>
       <c r="D102" s="3" t="s">
@@ -3754,10 +4201,10 @@
       <c r="A103" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="7" t="s">
         <v>107</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -3768,10 +4215,10 @@
       <c r="A104" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D104" s="3" t="s">
@@ -3782,10 +4229,10 @@
       <c r="A105" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D105" s="3" t="s">
@@ -3796,10 +4243,10 @@
       <c r="A106" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="7" t="s">
         <v>46</v>
       </c>
       <c r="D106" s="3" t="s">
@@ -3810,10 +4257,10 @@
       <c r="A107" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B107" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="7" t="s">
         <v>314</v>
       </c>
       <c r="D107" s="3" t="s">
@@ -3824,10 +4271,10 @@
       <c r="A108" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="B108" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D108" s="3" t="s">
@@ -3838,10 +4285,10 @@
       <c r="A109" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="7" t="s">
         <v>107</v>
       </c>
       <c r="D109" s="3" t="s">
@@ -3852,10 +4299,10 @@
       <c r="A110" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="7" t="s">
         <v>81</v>
       </c>
       <c r="D110" s="3" t="s">
@@ -3866,10 +4313,10 @@
       <c r="A111" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D111" s="3" t="s">
@@ -3880,10 +4327,10 @@
       <c r="A112" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D112" s="3" t="s">
@@ -3894,10 +4341,10 @@
       <c r="A113" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D113" s="3" t="s">
@@ -3908,10 +4355,10 @@
       <c r="A114" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D114" s="3" t="s">
@@ -3922,10 +4369,10 @@
       <c r="A115" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="7" t="s">
         <v>217</v>
       </c>
       <c r="D115" s="3" t="s">
@@ -3936,10 +4383,10 @@
       <c r="A116" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="7" t="s">
         <v>243</v>
       </c>
       <c r="D116" s="3" t="s">
@@ -3950,10 +4397,10 @@
       <c r="A117" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="7" t="s">
         <v>339</v>
       </c>
       <c r="D117" s="3" t="s">
@@ -3964,10 +4411,10 @@
       <c r="A118" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="7" t="s">
         <v>126</v>
       </c>
       <c r="D118" s="3" t="s">
@@ -3978,10 +4425,10 @@
       <c r="A119" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="7" t="s">
         <v>166</v>
       </c>
       <c r="D119" s="3" t="s">
@@ -3992,10 +4439,10 @@
       <c r="A120" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="7" t="s">
         <v>262</v>
       </c>
       <c r="D120" s="3" t="s">
@@ -4006,10 +4453,10 @@
       <c r="A121" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D121" s="3" t="s">
@@ -4020,10 +4467,10 @@
       <c r="A122" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="7" t="s">
         <v>351</v>
       </c>
       <c r="D122" s="3" t="s">
@@ -4034,7 +4481,7 @@
       <c r="A123" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="7" t="s">
         <v>148</v>
       </c>
       <c r="D123" s="3" t="s">
@@ -4045,7 +4492,7 @@
       <c r="A124" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="7" t="s">
         <v>356</v>
       </c>
       <c r="D124" s="3" t="s">
@@ -4056,10 +4503,10 @@
       <c r="A125" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D125" s="3" t="s">
@@ -4070,10 +4517,10 @@
       <c r="A126" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="7" t="s">
         <v>155</v>
       </c>
       <c r="D126" s="3" t="s">
@@ -4084,10 +4531,10 @@
       <c r="A127" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="7" t="s">
         <v>132</v>
       </c>
       <c r="D127" s="3" t="s">
@@ -4098,10 +4545,10 @@
       <c r="A128" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="7" t="s">
         <v>368</v>
       </c>
       <c r="D128" s="3" t="s">
@@ -4112,10 +4559,10 @@
       <c r="A129" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="7" t="s">
         <v>170</v>
       </c>
       <c r="D129" s="3" t="s">
@@ -4123,16 +4570,16 @@
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:4">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="7" t="s">
         <v>374</v>
       </c>
     </row>
@@ -4143,4 +4590,4056 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="13.95" spans="1:3">
+      <c r="B1" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="2" ht="14.55" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" ht="14.55" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" ht="14.55" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" ht="14.55" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" ht="14.55" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" ht="14.55" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" ht="14.55" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" ht="14.55" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" ht="14.55" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" ht="14.55" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="14.55" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="13" ht="14.55" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" ht="14.55" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" ht="14.55" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" ht="14.55" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" ht="14.55" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" ht="14.55" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" ht="14.55" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" ht="14.55" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" ht="14.55" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" ht="14.55" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" ht="14.55" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" ht="14.55" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" ht="14.55" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" ht="14.55" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="27" ht="14.55" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" ht="14.55" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" ht="14.55" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="30" ht="14.55" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" ht="14.55" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" ht="14.55" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" ht="14.55" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" ht="14.55" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="35" ht="14.55" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" ht="14.55" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" ht="14.55" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" ht="14.55" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" ht="14.55" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="40" ht="14.55" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" ht="14.55" spans="1:3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" ht="14.55" spans="1:3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" ht="14.55" spans="1:3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="44" ht="14.55" spans="1:3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" ht="14.55" spans="1:3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" ht="14.55" spans="1:3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" ht="14.55" spans="1:3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="48" ht="14.55" spans="1:3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" ht="14.55" spans="1:3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="50" ht="14.55" spans="1:3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" ht="14.55" spans="1:3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" ht="14.55" spans="1:3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" ht="14.55" spans="1:3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" ht="14.55" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" ht="14.55" spans="1:3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" ht="14.55" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="57" ht="14.55" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" ht="14.55" spans="1:3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="59" ht="14.55" spans="1:3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="60" ht="14.55" spans="1:3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="61" ht="14.55" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="62" ht="14.55" spans="1:3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" ht="14.55" spans="1:3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="64" ht="14.55" spans="1:3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="65" ht="14.55" spans="1:3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" ht="14.55" spans="1:3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" ht="14.55" spans="1:3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" ht="14.55" spans="1:3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" ht="14.55" spans="1:3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="70" ht="14.55" spans="1:3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" ht="14.55" spans="1:3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="72" ht="14.55" spans="1:3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="73" ht="14.55" spans="1:3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" ht="14.55" spans="1:3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="75" ht="14.55" spans="1:3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" ht="14.55" spans="1:3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" ht="14.55" spans="1:3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="78" ht="14.55" spans="1:3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="79" ht="14.55" spans="1:3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" ht="14.55" spans="1:3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" ht="14.55" spans="1:3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="82" ht="14.55" spans="1:3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="83" ht="14.55" spans="1:3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="84" ht="14.55" spans="1:3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" ht="14.55" spans="1:3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" ht="14.55" spans="1:3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" ht="14.55" spans="1:3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" ht="14.55" spans="1:3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="89" ht="14.55" spans="1:3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90" ht="14.55" spans="1:3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" ht="14.55" spans="1:3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" ht="14.55" spans="1:3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="93" ht="14.55" spans="1:3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="94" ht="14.55" spans="1:3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" ht="14.55" spans="1:3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="96" ht="14.55" spans="1:3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" ht="14.55" spans="1:3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="98" ht="14.55" spans="1:3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99" ht="14.55" spans="1:3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" ht="14.55" spans="1:3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="101" ht="14.55" spans="1:3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" ht="14.55" spans="1:3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="103" ht="14.55" spans="1:3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="104" ht="14.55" spans="1:3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="105" ht="14.55" spans="1:3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="106" ht="14.55" spans="1:3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="107" ht="14.55" spans="1:3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="108" ht="14.55" spans="1:3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="109" ht="14.55" spans="1:3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="110" ht="14.55" spans="1:3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" ht="14.55" spans="1:3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="112" ht="14.55" spans="1:3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="113" ht="14.55" spans="1:3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="114" ht="14.55" spans="1:3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="115" ht="14.55" spans="1:3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="116" ht="14.55" spans="1:3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117" ht="14.55" spans="1:3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118" ht="14.55" spans="1:3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="119" ht="14.55" spans="1:3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="120" ht="14.55" spans="1:3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="121" ht="14.55" spans="1:3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="122" ht="14.55" spans="1:3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="123" ht="14.55" spans="1:3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="124" ht="14.55" spans="1:3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="125" ht="14.55" spans="1:3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="126" ht="14.55" spans="1:3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="127" ht="14.55" spans="1:3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="128" ht="14.55" spans="1:3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="129" ht="14.55" spans="1:3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="130" ht="14.55" spans="1:3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="131" ht="13.95" spans="1:3">
+      <c r="B131" s="11"/>
+    </row>
+    <row r="132" ht="13.95" spans="1:3">
+      <c r="B132" s="11"/>
+    </row>
+    <row r="133" ht="13.95" spans="1:3">
+      <c r="B133" s="11"/>
+    </row>
+    <row r="134" ht="13.95" spans="1:3">
+      <c r="B134" s="11"/>
+    </row>
+    <row r="135" ht="13.95" spans="1:3">
+      <c r="B135" s="11"/>
+    </row>
+    <row r="136" ht="13.95" spans="1:3">
+      <c r="B136" s="11"/>
+    </row>
+    <row r="137" ht="13.95" spans="1:3">
+      <c r="B137" s="11"/>
+    </row>
+    <row r="138" ht="13.95" spans="1:3">
+      <c r="B138" s="11"/>
+    </row>
+    <row r="139" ht="13.95" spans="1:3">
+      <c r="B139" s="11"/>
+    </row>
+    <row r="140" ht="13.95" spans="1:3">
+      <c r="B140" s="11"/>
+    </row>
+    <row r="141" ht="13.95" spans="1:3">
+      <c r="B141" s="11"/>
+    </row>
+    <row r="142" ht="13.95" spans="1:3">
+      <c r="B142" s="11"/>
+    </row>
+    <row r="143" ht="13.95" spans="1:3">
+      <c r="B143" s="11"/>
+    </row>
+    <row r="144" ht="13.95" spans="1:3">
+      <c r="B144" s="11"/>
+    </row>
+    <row r="145" ht="13.95" spans="2:2">
+      <c r="B145" s="11"/>
+    </row>
+    <row r="146" ht="13.95" spans="2:2">
+      <c r="B146" s="11"/>
+    </row>
+    <row r="147" ht="13.95" spans="2:2">
+      <c r="B147" s="11"/>
+    </row>
+    <row r="148" ht="13.95" spans="2:2">
+      <c r="B148" s="11"/>
+    </row>
+    <row r="149" ht="13.95" spans="2:2">
+      <c r="B149" s="11"/>
+    </row>
+    <row r="150" ht="13.95" spans="2:2">
+      <c r="B150" s="11"/>
+    </row>
+    <row r="151" ht="13.95" spans="2:2">
+      <c r="B151" s="11"/>
+    </row>
+    <row r="152" ht="13.95" spans="2:2">
+      <c r="B152" s="11"/>
+    </row>
+    <row r="153" ht="13.95" spans="2:2">
+      <c r="B153" s="11"/>
+    </row>
+    <row r="154" ht="13.95" spans="2:2">
+      <c r="B154" s="11"/>
+    </row>
+    <row r="155" ht="13.95" spans="2:2">
+      <c r="B155" s="11"/>
+    </row>
+    <row r="156" ht="13.95" spans="2:2">
+      <c r="B156" s="11"/>
+    </row>
+    <row r="157" ht="13.95" spans="2:2">
+      <c r="B157" s="11"/>
+    </row>
+    <row r="158" ht="13.95" spans="2:2">
+      <c r="B158" s="11"/>
+    </row>
+    <row r="159" ht="13.95" spans="2:2">
+      <c r="B159" s="11"/>
+    </row>
+    <row r="160" ht="13.95" spans="2:2">
+      <c r="B160" s="11"/>
+    </row>
+    <row r="161" ht="13.95" spans="2:2">
+      <c r="B161" s="11"/>
+    </row>
+    <row r="162" ht="13.95" spans="2:2">
+      <c r="B162" s="11"/>
+    </row>
+    <row r="163" ht="13.95" spans="2:2">
+      <c r="B163" s="11"/>
+    </row>
+    <row r="164" ht="13.95" spans="2:2">
+      <c r="B164" s="11"/>
+    </row>
+    <row r="165" ht="13.95" spans="2:2">
+      <c r="B165" s="11"/>
+    </row>
+    <row r="166" ht="13.95" spans="2:2">
+      <c r="B166" s="11"/>
+    </row>
+    <row r="167" ht="13.95" spans="2:2">
+      <c r="B167" s="11"/>
+    </row>
+    <row r="168" ht="13.95" spans="2:2">
+      <c r="B168" s="11"/>
+    </row>
+    <row r="169" ht="13.95" spans="2:2">
+      <c r="B169" s="11"/>
+    </row>
+    <row r="170" ht="13.95" spans="2:2">
+      <c r="B170" s="11"/>
+    </row>
+    <row r="171" ht="13.95" spans="2:2">
+      <c r="B171" s="11"/>
+    </row>
+    <row r="172" ht="13.95" spans="2:2">
+      <c r="B172" s="11"/>
+    </row>
+    <row r="173" ht="13.95" spans="2:2">
+      <c r="B173" s="11"/>
+    </row>
+    <row r="174" ht="13.95" spans="2:2">
+      <c r="B174" s="11"/>
+    </row>
+    <row r="175" ht="13.95" spans="2:2">
+      <c r="B175" s="11"/>
+    </row>
+    <row r="176" ht="13.95" spans="2:2">
+      <c r="B176" s="11"/>
+    </row>
+    <row r="177" ht="13.95" spans="2:2">
+      <c r="B177" s="11"/>
+    </row>
+    <row r="178" ht="13.95" spans="2:2">
+      <c r="B178" s="11"/>
+    </row>
+    <row r="179" ht="13.95" spans="2:2">
+      <c r="B179" s="11"/>
+    </row>
+    <row r="180" ht="13.95" spans="2:2">
+      <c r="B180" s="11"/>
+    </row>
+    <row r="181" ht="13.95" spans="2:2">
+      <c r="B181" s="11"/>
+    </row>
+    <row r="182" ht="13.95" spans="2:2">
+      <c r="B182" s="11"/>
+    </row>
+    <row r="183" ht="13.95" spans="2:2">
+      <c r="B183" s="11"/>
+    </row>
+    <row r="184" ht="13.95" spans="2:2">
+      <c r="B184" s="11"/>
+    </row>
+    <row r="185" ht="13.95" spans="2:2">
+      <c r="B185" s="11"/>
+    </row>
+    <row r="186" ht="13.95" spans="2:2">
+      <c r="B186" s="11"/>
+    </row>
+    <row r="187" ht="13.95" spans="2:2">
+      <c r="B187" s="11"/>
+    </row>
+    <row r="188" ht="13.95" spans="2:2">
+      <c r="B188" s="11"/>
+    </row>
+    <row r="189" ht="13.95" spans="2:2">
+      <c r="B189" s="11"/>
+    </row>
+    <row r="190" ht="13.95" spans="2:2">
+      <c r="B190" s="11"/>
+    </row>
+    <row r="191" ht="13.95" spans="2:2">
+      <c r="B191" s="11"/>
+    </row>
+    <row r="192" ht="13.95" spans="2:2">
+      <c r="B192" s="11"/>
+    </row>
+    <row r="193" ht="13.95" spans="2:2">
+      <c r="B193" s="11"/>
+    </row>
+    <row r="194" ht="13.95" spans="2:2">
+      <c r="B194" s="11"/>
+    </row>
+    <row r="195" ht="13.95" spans="2:2">
+      <c r="B195" s="11"/>
+    </row>
+    <row r="196" ht="13.95" spans="2:2">
+      <c r="B196" s="11"/>
+    </row>
+    <row r="197" ht="13.95" spans="2:2">
+      <c r="B197" s="11"/>
+    </row>
+    <row r="198" ht="13.95" spans="2:2">
+      <c r="B198" s="11"/>
+    </row>
+    <row r="199" ht="13.95" spans="2:2">
+      <c r="B199" s="11"/>
+    </row>
+    <row r="200" ht="13.95" spans="2:2">
+      <c r="B200" s="11"/>
+    </row>
+    <row r="201" ht="13.95" spans="2:2">
+      <c r="B201" s="11"/>
+    </row>
+    <row r="202" ht="13.95" spans="2:2">
+      <c r="B202" s="11"/>
+    </row>
+    <row r="203" ht="13.95" spans="2:2">
+      <c r="B203" s="11"/>
+    </row>
+    <row r="204" ht="13.95" spans="2:2">
+      <c r="B204" s="11"/>
+    </row>
+    <row r="205" ht="13.95" spans="2:2">
+      <c r="B205" s="11"/>
+    </row>
+    <row r="206" ht="13.95" spans="2:2">
+      <c r="B206" s="11"/>
+    </row>
+    <row r="207" ht="13.95" spans="2:2">
+      <c r="B207" s="11"/>
+    </row>
+    <row r="208" ht="13.95" spans="2:2">
+      <c r="B208" s="11"/>
+    </row>
+    <row r="209" ht="13.95" spans="2:2">
+      <c r="B209" s="11"/>
+    </row>
+    <row r="210" ht="13.95" spans="2:2">
+      <c r="B210" s="11"/>
+    </row>
+    <row r="211" ht="13.95" spans="2:2">
+      <c r="B211" s="11"/>
+    </row>
+    <row r="212" ht="13.95" spans="2:2">
+      <c r="B212" s="11"/>
+    </row>
+    <row r="213" ht="13.95" spans="2:2">
+      <c r="B213" s="11"/>
+    </row>
+    <row r="214" ht="13.95" spans="2:2">
+      <c r="B214" s="11"/>
+    </row>
+    <row r="215" ht="13.95" spans="2:2">
+      <c r="B215" s="11"/>
+    </row>
+    <row r="216" ht="13.95" spans="2:2">
+      <c r="B216" s="11"/>
+    </row>
+    <row r="217" ht="13.95" spans="2:2">
+      <c r="B217" s="11"/>
+    </row>
+    <row r="218" ht="13.95" spans="2:2">
+      <c r="B218" s="11"/>
+    </row>
+    <row r="219" ht="13.95" spans="2:2">
+      <c r="B219" s="11"/>
+    </row>
+    <row r="220" ht="13.95" spans="2:2">
+      <c r="B220" s="11"/>
+    </row>
+    <row r="221" ht="13.95" spans="2:2">
+      <c r="B221" s="11"/>
+    </row>
+    <row r="222" ht="13.95" spans="2:2">
+      <c r="B222" s="11"/>
+    </row>
+    <row r="223" ht="13.95" spans="2:2">
+      <c r="B223" s="11"/>
+    </row>
+    <row r="224" ht="13.95" spans="2:2">
+      <c r="B224" s="11"/>
+    </row>
+    <row r="225" ht="13.95" spans="2:2">
+      <c r="B225" s="11"/>
+    </row>
+    <row r="226" ht="13.95" spans="2:2">
+      <c r="B226" s="11"/>
+    </row>
+    <row r="227" ht="13.95" spans="2:2">
+      <c r="B227" s="11"/>
+    </row>
+    <row r="228" ht="13.95" spans="2:2">
+      <c r="B228" s="11"/>
+    </row>
+    <row r="229" ht="13.95" spans="2:2">
+      <c r="B229" s="11"/>
+    </row>
+    <row r="230" ht="13.95" spans="2:2">
+      <c r="B230" s="11"/>
+    </row>
+    <row r="231" ht="13.95" spans="2:2">
+      <c r="B231" s="11"/>
+    </row>
+    <row r="232" ht="13.95" spans="2:2">
+      <c r="B232" s="11"/>
+    </row>
+    <row r="233" ht="13.95" spans="2:2">
+      <c r="B233" s="11"/>
+    </row>
+    <row r="234" ht="13.95" spans="2:2">
+      <c r="B234" s="11"/>
+    </row>
+    <row r="235" ht="13.95" spans="2:2">
+      <c r="B235" s="11"/>
+    </row>
+    <row r="236" ht="13.95" spans="2:2">
+      <c r="B236" s="11"/>
+    </row>
+    <row r="237" ht="13.95" spans="2:2">
+      <c r="B237" s="11"/>
+    </row>
+    <row r="238" ht="13.95" spans="2:2">
+      <c r="B238" s="11"/>
+    </row>
+    <row r="239" ht="13.95" spans="2:2">
+      <c r="B239" s="11"/>
+    </row>
+    <row r="240" ht="13.95" spans="2:2">
+      <c r="B240" s="11"/>
+    </row>
+    <row r="241" ht="13.95" spans="2:2">
+      <c r="B241" s="11"/>
+    </row>
+    <row r="242" ht="13.95" spans="2:2">
+      <c r="B242" s="11"/>
+    </row>
+    <row r="243" ht="13.95" spans="2:2">
+      <c r="B243" s="11"/>
+    </row>
+    <row r="244" ht="13.95" spans="2:2">
+      <c r="B244" s="11"/>
+    </row>
+    <row r="245" ht="13.95" spans="2:2">
+      <c r="B245" s="11"/>
+    </row>
+    <row r="246" ht="13.95" spans="2:2">
+      <c r="B246" s="11"/>
+    </row>
+    <row r="247" ht="13.95" spans="2:2">
+      <c r="B247" s="11"/>
+    </row>
+    <row r="248" ht="13.95" spans="2:2">
+      <c r="B248" s="11"/>
+    </row>
+    <row r="249" ht="13.95" spans="2:2">
+      <c r="B249" s="11"/>
+    </row>
+    <row r="250" ht="13.95" spans="2:2">
+      <c r="B250" s="11"/>
+    </row>
+    <row r="251" ht="13.95" spans="2:2">
+      <c r="B251" s="11"/>
+    </row>
+    <row r="252" ht="13.95" spans="2:2">
+      <c r="B252" s="11"/>
+    </row>
+    <row r="253" ht="13.95" spans="2:2">
+      <c r="B253" s="11"/>
+    </row>
+    <row r="254" ht="13.95" spans="2:2">
+      <c r="B254" s="11"/>
+    </row>
+    <row r="255" ht="13.95" spans="2:2">
+      <c r="B255" s="11"/>
+    </row>
+    <row r="256" ht="13.95" spans="2:2">
+      <c r="B256" s="11"/>
+    </row>
+    <row r="257" ht="13.95" spans="2:2">
+      <c r="B257" s="11"/>
+    </row>
+    <row r="258" ht="13.95" spans="2:2">
+      <c r="B258" s="11"/>
+    </row>
+    <row r="259" ht="13.95" spans="2:2">
+      <c r="B259" s="11"/>
+    </row>
+    <row r="260" ht="13.95" spans="2:2">
+      <c r="B260" s="11"/>
+    </row>
+    <row r="261" ht="13.95" spans="2:2">
+      <c r="B261" s="11"/>
+    </row>
+    <row r="262" ht="13.95" spans="2:2">
+      <c r="B262" s="11"/>
+    </row>
+    <row r="263" ht="13.95" spans="2:2">
+      <c r="B263" s="11"/>
+    </row>
+    <row r="264" ht="13.95" spans="2:2">
+      <c r="B264" s="11"/>
+    </row>
+    <row r="265" ht="13.95" spans="2:2">
+      <c r="B265" s="11"/>
+    </row>
+    <row r="266" ht="13.95" spans="2:2">
+      <c r="B266" s="11"/>
+    </row>
+    <row r="267" ht="13.95" spans="2:2">
+      <c r="B267" s="11"/>
+    </row>
+    <row r="268" ht="13.95" spans="2:2">
+      <c r="B268" s="11"/>
+    </row>
+    <row r="269" ht="13.95" spans="2:2">
+      <c r="B269" s="11"/>
+    </row>
+    <row r="270" ht="13.95" spans="2:2">
+      <c r="B270" s="11"/>
+    </row>
+    <row r="271" ht="13.95" spans="2:2">
+      <c r="B271" s="11"/>
+    </row>
+    <row r="272" ht="13.95" spans="2:2">
+      <c r="B272" s="11"/>
+    </row>
+    <row r="273" ht="13.95" spans="2:2">
+      <c r="B273" s="11"/>
+    </row>
+    <row r="274" ht="13.95" spans="2:2">
+      <c r="B274" s="11"/>
+    </row>
+    <row r="275" ht="13.95" spans="2:2">
+      <c r="B275" s="11"/>
+    </row>
+    <row r="276" ht="13.95" spans="2:2">
+      <c r="B276" s="11"/>
+    </row>
+    <row r="277" ht="13.95" spans="2:2">
+      <c r="B277" s="11"/>
+    </row>
+    <row r="278" ht="13.95" spans="2:2">
+      <c r="B278" s="11"/>
+    </row>
+    <row r="279" ht="13.95" spans="2:2">
+      <c r="B279" s="11"/>
+    </row>
+    <row r="280" ht="13.95" spans="2:2">
+      <c r="B280" s="11"/>
+    </row>
+    <row r="281" ht="13.95" spans="2:2">
+      <c r="B281" s="11"/>
+    </row>
+    <row r="282" ht="13.95" spans="2:2">
+      <c r="B282" s="11"/>
+    </row>
+    <row r="283" ht="13.95" spans="2:2">
+      <c r="B283" s="11"/>
+    </row>
+    <row r="284" ht="13.95" spans="2:2">
+      <c r="B284" s="11"/>
+    </row>
+    <row r="285" ht="13.95" spans="2:2">
+      <c r="B285" s="11"/>
+    </row>
+    <row r="286" ht="13.95" spans="2:2">
+      <c r="B286" s="11"/>
+    </row>
+    <row r="287" ht="13.95" spans="2:2">
+      <c r="B287" s="11"/>
+    </row>
+    <row r="288" ht="13.95" spans="2:2">
+      <c r="B288" s="11"/>
+    </row>
+    <row r="289" ht="13.95" spans="2:2">
+      <c r="B289" s="11"/>
+    </row>
+    <row r="290" ht="13.95" spans="2:2">
+      <c r="B290" s="11"/>
+    </row>
+    <row r="291" ht="13.95" spans="2:2">
+      <c r="B291" s="11"/>
+    </row>
+    <row r="292" ht="13.95" spans="2:2">
+      <c r="B292" s="11"/>
+    </row>
+    <row r="293" ht="13.95" spans="2:2">
+      <c r="B293" s="11"/>
+    </row>
+    <row r="294" ht="13.95" spans="2:2">
+      <c r="B294" s="11"/>
+    </row>
+    <row r="295" ht="13.95" spans="2:2">
+      <c r="B295" s="11"/>
+    </row>
+    <row r="296" ht="13.95" spans="2:2">
+      <c r="B296" s="11"/>
+    </row>
+    <row r="297" ht="13.95" spans="2:2">
+      <c r="B297" s="11"/>
+    </row>
+    <row r="298" ht="13.95" spans="2:2">
+      <c r="B298" s="11"/>
+    </row>
+    <row r="299" ht="13.95" spans="2:2">
+      <c r="B299" s="11"/>
+    </row>
+    <row r="300" ht="13.95" spans="2:2">
+      <c r="B300" s="11"/>
+    </row>
+    <row r="301" ht="13.95" spans="2:2">
+      <c r="B301" s="11"/>
+    </row>
+    <row r="302" ht="13.95" spans="2:2">
+      <c r="B302" s="11"/>
+    </row>
+    <row r="303" ht="13.95" spans="2:2">
+      <c r="B303" s="11"/>
+    </row>
+    <row r="304" ht="13.95" spans="2:2">
+      <c r="B304" s="11"/>
+    </row>
+    <row r="305" ht="13.95" spans="2:2">
+      <c r="B305" s="11"/>
+    </row>
+    <row r="306" ht="13.95" spans="2:2">
+      <c r="B306" s="11"/>
+    </row>
+    <row r="307" ht="13.95" spans="2:2">
+      <c r="B307" s="11"/>
+    </row>
+    <row r="308" ht="13.95" spans="2:2">
+      <c r="B308" s="11"/>
+    </row>
+    <row r="309" ht="13.95" spans="2:2">
+      <c r="B309" s="11"/>
+    </row>
+    <row r="310" ht="13.95" spans="2:2">
+      <c r="B310" s="11"/>
+    </row>
+    <row r="311" ht="13.95" spans="2:2">
+      <c r="B311" s="11"/>
+    </row>
+    <row r="312" ht="13.95" spans="2:2">
+      <c r="B312" s="11"/>
+    </row>
+    <row r="313" ht="13.95" spans="2:2">
+      <c r="B313" s="11"/>
+    </row>
+    <row r="314" ht="13.95" spans="2:2">
+      <c r="B314" s="11"/>
+    </row>
+    <row r="315" ht="13.95" spans="2:2">
+      <c r="B315" s="11"/>
+    </row>
+    <row r="316" ht="13.95" spans="2:2">
+      <c r="B316" s="11"/>
+    </row>
+    <row r="317" ht="13.95" spans="2:2">
+      <c r="B317" s="11"/>
+    </row>
+    <row r="318" ht="13.95" spans="2:2">
+      <c r="B318" s="11"/>
+    </row>
+    <row r="319" ht="13.95" spans="2:2">
+      <c r="B319" s="11"/>
+    </row>
+    <row r="320" ht="13.95" spans="2:2">
+      <c r="B320" s="11"/>
+    </row>
+    <row r="321" ht="13.95" spans="2:2">
+      <c r="B321" s="11"/>
+    </row>
+    <row r="322" ht="13.95" spans="2:2">
+      <c r="B322" s="11"/>
+    </row>
+    <row r="323" ht="13.95" spans="2:2">
+      <c r="B323" s="11"/>
+    </row>
+    <row r="324" ht="13.95" spans="2:2">
+      <c r="B324" s="11"/>
+    </row>
+    <row r="325" ht="13.95" spans="2:2">
+      <c r="B325" s="11"/>
+    </row>
+    <row r="326" ht="13.95" spans="2:2">
+      <c r="B326" s="11"/>
+    </row>
+    <row r="327" ht="13.95" spans="2:2">
+      <c r="B327" s="11"/>
+    </row>
+    <row r="328" ht="13.95" spans="2:2">
+      <c r="B328" s="11"/>
+    </row>
+    <row r="329" ht="13.95" spans="2:2">
+      <c r="B329" s="11"/>
+    </row>
+    <row r="330" ht="13.95" spans="2:2">
+      <c r="B330" s="11"/>
+    </row>
+    <row r="331" ht="13.95" spans="2:2">
+      <c r="B331" s="11"/>
+    </row>
+    <row r="332" ht="13.95" spans="2:2">
+      <c r="B332" s="11"/>
+    </row>
+    <row r="333" ht="13.95" spans="2:2">
+      <c r="B333" s="11"/>
+    </row>
+    <row r="334" ht="13.95" spans="2:2">
+      <c r="B334" s="11"/>
+    </row>
+    <row r="335" ht="13.95" spans="2:2">
+      <c r="B335" s="11"/>
+    </row>
+    <row r="336" ht="13.95" spans="2:2">
+      <c r="B336" s="11"/>
+    </row>
+    <row r="337" ht="13.95" spans="2:2">
+      <c r="B337" s="11"/>
+    </row>
+    <row r="338" ht="13.95" spans="2:2">
+      <c r="B338" s="11"/>
+    </row>
+    <row r="339" ht="13.95" spans="2:2">
+      <c r="B339" s="11"/>
+    </row>
+    <row r="340" ht="13.95" spans="2:2">
+      <c r="B340" s="11"/>
+    </row>
+    <row r="341" ht="13.95" spans="2:2">
+      <c r="B341" s="11"/>
+    </row>
+    <row r="342" ht="13.95" spans="2:2">
+      <c r="B342" s="11"/>
+    </row>
+    <row r="343" ht="13.95" spans="2:2">
+      <c r="B343" s="11"/>
+    </row>
+    <row r="344" ht="13.95" spans="2:2">
+      <c r="B344" s="11"/>
+    </row>
+    <row r="345" ht="13.95" spans="2:2">
+      <c r="B345" s="11"/>
+    </row>
+    <row r="346" ht="13.95" spans="2:2">
+      <c r="B346" s="11"/>
+    </row>
+    <row r="347" ht="13.95" spans="2:2">
+      <c r="B347" s="11"/>
+    </row>
+    <row r="348" ht="13.95" spans="2:2">
+      <c r="B348" s="11"/>
+    </row>
+    <row r="349" ht="13.95" spans="2:2">
+      <c r="B349" s="11"/>
+    </row>
+    <row r="350" ht="13.95" spans="2:2">
+      <c r="B350" s="11"/>
+    </row>
+    <row r="351" ht="13.95" spans="2:2">
+      <c r="B351" s="11"/>
+    </row>
+    <row r="352" ht="13.95" spans="2:2">
+      <c r="B352" s="11"/>
+    </row>
+    <row r="353" ht="13.95" spans="2:2">
+      <c r="B353" s="11"/>
+    </row>
+    <row r="354" ht="13.95" spans="2:2">
+      <c r="B354" s="11"/>
+    </row>
+    <row r="355" ht="13.95" spans="2:2">
+      <c r="B355" s="11"/>
+    </row>
+    <row r="356" ht="13.95" spans="2:2">
+      <c r="B356" s="11"/>
+    </row>
+    <row r="357" ht="13.95" spans="2:2">
+      <c r="B357" s="11"/>
+    </row>
+    <row r="358" ht="13.95" spans="2:2">
+      <c r="B358" s="11"/>
+    </row>
+    <row r="359" ht="13.95" spans="2:2">
+      <c r="B359" s="11"/>
+    </row>
+    <row r="360" ht="13.95" spans="2:2">
+      <c r="B360" s="11"/>
+    </row>
+    <row r="361" ht="13.95" spans="2:2">
+      <c r="B361" s="11"/>
+    </row>
+    <row r="362" ht="13.95" spans="2:2">
+      <c r="B362" s="11"/>
+    </row>
+    <row r="363" ht="13.95" spans="2:2">
+      <c r="B363" s="11"/>
+    </row>
+    <row r="364" ht="13.95" spans="2:2">
+      <c r="B364" s="11"/>
+    </row>
+    <row r="365" ht="13.95" spans="2:2">
+      <c r="B365" s="11"/>
+    </row>
+    <row r="366" ht="13.95" spans="2:2">
+      <c r="B366" s="11"/>
+    </row>
+    <row r="367" ht="13.95" spans="2:2">
+      <c r="B367" s="11"/>
+    </row>
+    <row r="368" ht="13.95" spans="2:2">
+      <c r="B368" s="11"/>
+    </row>
+    <row r="369" ht="13.95" spans="2:2">
+      <c r="B369" s="11"/>
+    </row>
+    <row r="370" ht="13.95" spans="2:2">
+      <c r="B370" s="11"/>
+    </row>
+    <row r="371" ht="13.95" spans="2:2">
+      <c r="B371" s="11"/>
+    </row>
+    <row r="372" ht="13.95" spans="2:2">
+      <c r="B372" s="11"/>
+    </row>
+    <row r="373" ht="13.95" spans="2:2">
+      <c r="B373" s="11"/>
+    </row>
+    <row r="374" ht="13.95" spans="2:2">
+      <c r="B374" s="11"/>
+    </row>
+    <row r="375" ht="13.95" spans="2:2">
+      <c r="B375" s="11"/>
+    </row>
+    <row r="376" ht="13.95" spans="2:2">
+      <c r="B376" s="11"/>
+    </row>
+    <row r="377" ht="13.95" spans="2:2">
+      <c r="B377" s="11"/>
+    </row>
+    <row r="378" ht="13.95" spans="2:2">
+      <c r="B378" s="11"/>
+    </row>
+    <row r="379" ht="13.95" spans="2:2">
+      <c r="B379" s="11"/>
+    </row>
+    <row r="380" ht="13.95" spans="2:2">
+      <c r="B380" s="11"/>
+    </row>
+    <row r="381" ht="13.95" spans="2:2">
+      <c r="B381" s="11"/>
+    </row>
+    <row r="382" ht="13.95" spans="2:2">
+      <c r="B382" s="11"/>
+    </row>
+    <row r="383" ht="13.95" spans="2:2">
+      <c r="B383" s="11"/>
+    </row>
+    <row r="384" ht="13.95" spans="2:2">
+      <c r="B384" s="11"/>
+    </row>
+    <row r="385" ht="13.95" spans="2:2">
+      <c r="B385" s="11"/>
+    </row>
+    <row r="386" ht="13.95" spans="2:2">
+      <c r="B386" s="11"/>
+    </row>
+    <row r="387" ht="13.95" spans="2:2">
+      <c r="B387" s="11"/>
+    </row>
+    <row r="388" ht="13.95" spans="2:2">
+      <c r="B388" s="11"/>
+    </row>
+    <row r="389" ht="13.95" spans="2:2">
+      <c r="B389" s="11"/>
+    </row>
+    <row r="390" ht="13.95" spans="2:2">
+      <c r="B390" s="11"/>
+    </row>
+    <row r="391" ht="13.95" spans="2:2">
+      <c r="B391" s="11"/>
+    </row>
+    <row r="392" ht="13.95" spans="2:2">
+      <c r="B392" s="11"/>
+    </row>
+    <row r="393" ht="13.95" spans="2:2">
+      <c r="B393" s="11"/>
+    </row>
+    <row r="394" ht="13.95" spans="2:2">
+      <c r="B394" s="11"/>
+    </row>
+    <row r="395" ht="13.95" spans="2:2">
+      <c r="B395" s="11"/>
+    </row>
+    <row r="396" ht="13.95" spans="2:2">
+      <c r="B396" s="11"/>
+    </row>
+    <row r="397" ht="13.95" spans="2:2">
+      <c r="B397" s="11"/>
+    </row>
+    <row r="398" ht="13.95" spans="2:2">
+      <c r="B398" s="11"/>
+    </row>
+    <row r="399" ht="13.95" spans="2:2">
+      <c r="B399" s="11"/>
+    </row>
+    <row r="400" ht="13.95" spans="2:2">
+      <c r="B400" s="11"/>
+    </row>
+    <row r="401" ht="13.95" spans="2:2">
+      <c r="B401" s="11"/>
+    </row>
+    <row r="402" ht="13.95" spans="2:2">
+      <c r="B402" s="11"/>
+    </row>
+    <row r="403" ht="13.95" spans="2:2">
+      <c r="B403" s="11"/>
+    </row>
+    <row r="404" ht="13.95" spans="2:2">
+      <c r="B404" s="11"/>
+    </row>
+    <row r="405" ht="13.95" spans="2:2">
+      <c r="B405" s="11"/>
+    </row>
+    <row r="406" ht="13.95" spans="2:2">
+      <c r="B406" s="11"/>
+    </row>
+    <row r="407" ht="13.95" spans="2:2">
+      <c r="B407" s="11"/>
+    </row>
+    <row r="408" ht="13.95" spans="2:2">
+      <c r="B408" s="11"/>
+    </row>
+    <row r="409" ht="13.95" spans="2:2">
+      <c r="B409" s="11"/>
+    </row>
+    <row r="410" ht="13.95" spans="2:2">
+      <c r="B410" s="11"/>
+    </row>
+    <row r="411" ht="13.95" spans="2:2">
+      <c r="B411" s="11"/>
+    </row>
+    <row r="412" ht="13.95" spans="2:2">
+      <c r="B412" s="11"/>
+    </row>
+    <row r="413" ht="13.95" spans="2:2">
+      <c r="B413" s="11"/>
+    </row>
+    <row r="414" ht="13.95" spans="2:2">
+      <c r="B414" s="11"/>
+    </row>
+    <row r="415" ht="13.95" spans="2:2">
+      <c r="B415" s="11"/>
+    </row>
+    <row r="416" ht="13.95" spans="2:2">
+      <c r="B416" s="11"/>
+    </row>
+    <row r="417" ht="13.95" spans="2:2">
+      <c r="B417" s="11"/>
+    </row>
+    <row r="418" ht="13.95" spans="2:2">
+      <c r="B418" s="11"/>
+    </row>
+    <row r="419" ht="13.95" spans="2:2">
+      <c r="B419" s="11"/>
+    </row>
+    <row r="420" ht="13.95" spans="2:2">
+      <c r="B420" s="11"/>
+    </row>
+    <row r="421" ht="13.95" spans="2:2">
+      <c r="B421" s="11"/>
+    </row>
+    <row r="422" ht="13.95" spans="2:2">
+      <c r="B422" s="11"/>
+    </row>
+    <row r="423" ht="13.95" spans="2:2">
+      <c r="B423" s="11"/>
+    </row>
+    <row r="424" ht="13.95" spans="2:2">
+      <c r="B424" s="11"/>
+    </row>
+    <row r="425" ht="13.95" spans="2:2">
+      <c r="B425" s="11"/>
+    </row>
+    <row r="426" ht="13.95" spans="2:2">
+      <c r="B426" s="11"/>
+    </row>
+    <row r="427" ht="13.95" spans="2:2">
+      <c r="B427" s="11"/>
+    </row>
+    <row r="428" ht="13.95" spans="2:2">
+      <c r="B428" s="11"/>
+    </row>
+    <row r="429" ht="13.95" spans="2:2">
+      <c r="B429" s="11"/>
+    </row>
+    <row r="430" ht="13.95" spans="2:2">
+      <c r="B430" s="11"/>
+    </row>
+    <row r="431" ht="13.95" spans="2:2">
+      <c r="B431" s="11"/>
+    </row>
+    <row r="432" ht="13.95" spans="2:2">
+      <c r="B432" s="11"/>
+    </row>
+    <row r="433" ht="13.95" spans="2:2">
+      <c r="B433" s="11"/>
+    </row>
+    <row r="434" ht="13.95" spans="2:2">
+      <c r="B434" s="11"/>
+    </row>
+    <row r="435" ht="13.95" spans="2:2">
+      <c r="B435" s="11"/>
+    </row>
+    <row r="436" ht="13.95" spans="2:2">
+      <c r="B436" s="11"/>
+    </row>
+    <row r="437" ht="13.95" spans="2:2">
+      <c r="B437" s="11"/>
+    </row>
+    <row r="438" ht="13.95" spans="2:2">
+      <c r="B438" s="11"/>
+    </row>
+    <row r="439" ht="13.95" spans="2:2">
+      <c r="B439" s="11"/>
+    </row>
+    <row r="440" ht="13.95" spans="2:2">
+      <c r="B440" s="11"/>
+    </row>
+    <row r="441" ht="13.95" spans="2:2">
+      <c r="B441" s="11"/>
+    </row>
+    <row r="442" ht="13.95" spans="2:2">
+      <c r="B442" s="11"/>
+    </row>
+    <row r="443" ht="13.95" spans="2:2">
+      <c r="B443" s="11"/>
+    </row>
+    <row r="444" ht="13.95" spans="2:2">
+      <c r="B444" s="11"/>
+    </row>
+    <row r="445" ht="13.95" spans="2:2">
+      <c r="B445" s="11"/>
+    </row>
+    <row r="446" ht="13.95" spans="2:2">
+      <c r="B446" s="11"/>
+    </row>
+    <row r="447" ht="13.95" spans="2:2">
+      <c r="B447" s="11"/>
+    </row>
+    <row r="448" ht="13.95" spans="2:2">
+      <c r="B448" s="11"/>
+    </row>
+    <row r="449" ht="13.95" spans="2:2">
+      <c r="B449" s="11"/>
+    </row>
+    <row r="450" ht="13.95" spans="2:2">
+      <c r="B450" s="11"/>
+    </row>
+    <row r="451" ht="13.95" spans="2:2">
+      <c r="B451" s="11"/>
+    </row>
+    <row r="452" ht="13.95" spans="2:2">
+      <c r="B452" s="11"/>
+    </row>
+    <row r="453" ht="13.95" spans="2:2">
+      <c r="B453" s="11"/>
+    </row>
+    <row r="454" ht="13.95" spans="2:2">
+      <c r="B454" s="11"/>
+    </row>
+    <row r="455" ht="13.95" spans="2:2">
+      <c r="B455" s="11"/>
+    </row>
+    <row r="456" ht="13.95" spans="2:2">
+      <c r="B456" s="11"/>
+    </row>
+    <row r="457" ht="13.95" spans="2:2">
+      <c r="B457" s="11"/>
+    </row>
+    <row r="458" ht="13.95" spans="2:2">
+      <c r="B458" s="11"/>
+    </row>
+    <row r="459" ht="13.95" spans="2:2">
+      <c r="B459" s="11"/>
+    </row>
+    <row r="460" ht="13.95" spans="2:2">
+      <c r="B460" s="11"/>
+    </row>
+    <row r="461" ht="13.95" spans="2:2">
+      <c r="B461" s="11"/>
+    </row>
+    <row r="462" ht="13.95" spans="2:2">
+      <c r="B462" s="11"/>
+    </row>
+    <row r="463" ht="13.95" spans="2:2">
+      <c r="B463" s="11"/>
+    </row>
+    <row r="464" ht="13.95" spans="2:2">
+      <c r="B464" s="11"/>
+    </row>
+    <row r="465" ht="13.95" spans="2:2">
+      <c r="B465" s="11"/>
+    </row>
+    <row r="466" ht="13.95" spans="2:2">
+      <c r="B466" s="11"/>
+    </row>
+    <row r="467" ht="13.95" spans="2:2">
+      <c r="B467" s="11"/>
+    </row>
+    <row r="468" ht="13.95" spans="2:2">
+      <c r="B468" s="11"/>
+    </row>
+    <row r="469" ht="13.95" spans="2:2">
+      <c r="B469" s="11"/>
+    </row>
+    <row r="470" ht="13.95" spans="2:2">
+      <c r="B470" s="11"/>
+    </row>
+    <row r="471" ht="13.95" spans="2:2">
+      <c r="B471" s="11"/>
+    </row>
+    <row r="472" ht="13.95" spans="2:2">
+      <c r="B472" s="11"/>
+    </row>
+    <row r="473" ht="13.95" spans="2:2">
+      <c r="B473" s="11"/>
+    </row>
+    <row r="474" ht="13.95" spans="2:2">
+      <c r="B474" s="11"/>
+    </row>
+    <row r="475" ht="13.95" spans="2:2">
+      <c r="B475" s="11"/>
+    </row>
+    <row r="476" ht="13.95" spans="2:2">
+      <c r="B476" s="11"/>
+    </row>
+    <row r="477" ht="13.95" spans="2:2">
+      <c r="B477" s="11"/>
+    </row>
+    <row r="478" ht="13.95" spans="2:2">
+      <c r="B478" s="11"/>
+    </row>
+    <row r="479" ht="13.95" spans="2:2">
+      <c r="B479" s="11"/>
+    </row>
+    <row r="480" ht="13.95" spans="2:2">
+      <c r="B480" s="11"/>
+    </row>
+    <row r="481" ht="13.95" spans="2:2">
+      <c r="B481" s="11"/>
+    </row>
+    <row r="482" ht="13.95" spans="2:2">
+      <c r="B482" s="11"/>
+    </row>
+    <row r="483" ht="13.95" spans="2:2">
+      <c r="B483" s="11"/>
+    </row>
+    <row r="484" ht="13.95" spans="2:2">
+      <c r="B484" s="11"/>
+    </row>
+    <row r="485" ht="13.95" spans="2:2">
+      <c r="B485" s="11"/>
+    </row>
+    <row r="486" ht="13.95" spans="2:2">
+      <c r="B486" s="11"/>
+    </row>
+    <row r="487" ht="13.95" spans="2:2">
+      <c r="B487" s="11"/>
+    </row>
+    <row r="488" ht="13.95" spans="2:2">
+      <c r="B488" s="11"/>
+    </row>
+    <row r="489" ht="13.95" spans="2:2">
+      <c r="B489" s="11"/>
+    </row>
+    <row r="490" ht="13.95" spans="2:2">
+      <c r="B490" s="11"/>
+    </row>
+    <row r="491" ht="13.95" spans="2:2">
+      <c r="B491" s="11"/>
+    </row>
+    <row r="492" ht="13.95" spans="2:2">
+      <c r="B492" s="11"/>
+    </row>
+    <row r="493" ht="13.95" spans="2:2">
+      <c r="B493" s="11"/>
+    </row>
+    <row r="494" ht="13.95" spans="2:2">
+      <c r="B494" s="11"/>
+    </row>
+    <row r="495" ht="13.95" spans="2:2">
+      <c r="B495" s="11"/>
+    </row>
+    <row r="496" ht="13.95" spans="2:2">
+      <c r="B496" s="11"/>
+    </row>
+    <row r="497" ht="13.95" spans="2:2">
+      <c r="B497" s="11"/>
+    </row>
+    <row r="498" ht="13.95" spans="2:2">
+      <c r="B498" s="11"/>
+    </row>
+    <row r="499" ht="13.95" spans="2:2">
+      <c r="B499" s="11"/>
+    </row>
+    <row r="500" ht="13.95" spans="2:2">
+      <c r="B500" s="11"/>
+    </row>
+    <row r="501" ht="13.95" spans="2:2">
+      <c r="B501" s="11"/>
+    </row>
+    <row r="502" ht="13.95" spans="2:2">
+      <c r="B502" s="11"/>
+    </row>
+    <row r="503" ht="13.95" spans="2:2">
+      <c r="B503" s="11"/>
+    </row>
+    <row r="504" ht="13.95" spans="2:2">
+      <c r="B504" s="11"/>
+    </row>
+    <row r="505" ht="13.95" spans="2:2">
+      <c r="B505" s="11"/>
+    </row>
+    <row r="506" ht="13.95" spans="2:2">
+      <c r="B506" s="11"/>
+    </row>
+    <row r="507" ht="13.95" spans="2:2">
+      <c r="B507" s="11"/>
+    </row>
+    <row r="508" ht="13.95" spans="2:2">
+      <c r="B508" s="11"/>
+    </row>
+    <row r="509" ht="13.95" spans="2:2">
+      <c r="B509" s="11"/>
+    </row>
+    <row r="510" ht="13.95" spans="2:2">
+      <c r="B510" s="11"/>
+    </row>
+    <row r="511" ht="13.95" spans="2:2">
+      <c r="B511" s="11"/>
+    </row>
+    <row r="512" ht="13.95" spans="2:2">
+      <c r="B512" s="11"/>
+    </row>
+    <row r="513" ht="13.95" spans="2:2">
+      <c r="B513" s="11"/>
+    </row>
+    <row r="514" ht="13.95" spans="2:2">
+      <c r="B514" s="11"/>
+    </row>
+    <row r="515" ht="13.95" spans="2:2">
+      <c r="B515" s="11"/>
+    </row>
+    <row r="516" ht="13.95" spans="2:2">
+      <c r="B516" s="11"/>
+    </row>
+    <row r="517" ht="13.95" spans="2:2">
+      <c r="B517" s="11"/>
+    </row>
+    <row r="518" ht="13.95" spans="2:2">
+      <c r="B518" s="11"/>
+    </row>
+    <row r="519" ht="13.95" spans="2:2">
+      <c r="B519" s="11"/>
+    </row>
+    <row r="520" ht="13.95" spans="2:2">
+      <c r="B520" s="11"/>
+    </row>
+    <row r="521" ht="13.95" spans="2:2">
+      <c r="B521" s="11"/>
+    </row>
+    <row r="522" ht="13.95" spans="2:2">
+      <c r="B522" s="11"/>
+    </row>
+    <row r="523" ht="13.95" spans="2:2">
+      <c r="B523" s="11"/>
+    </row>
+    <row r="524" ht="13.95" spans="2:2">
+      <c r="B524" s="11"/>
+    </row>
+    <row r="525" ht="13.95" spans="2:2">
+      <c r="B525" s="11"/>
+    </row>
+    <row r="526" ht="13.95" spans="2:2">
+      <c r="B526" s="11"/>
+    </row>
+    <row r="527" ht="13.95" spans="2:2">
+      <c r="B527" s="11"/>
+    </row>
+    <row r="528" ht="13.95" spans="2:2">
+      <c r="B528" s="11"/>
+    </row>
+    <row r="529" ht="13.95" spans="2:2">
+      <c r="B529" s="11"/>
+    </row>
+    <row r="530" ht="13.95" spans="2:2">
+      <c r="B530" s="11"/>
+    </row>
+    <row r="531" ht="13.95" spans="2:2">
+      <c r="B531" s="11"/>
+    </row>
+    <row r="532" ht="13.95" spans="2:2">
+      <c r="B532" s="11"/>
+    </row>
+    <row r="533" ht="13.95" spans="2:2">
+      <c r="B533" s="11"/>
+    </row>
+    <row r="534" ht="13.95" spans="2:2">
+      <c r="B534" s="11"/>
+    </row>
+    <row r="535" ht="13.95" spans="2:2">
+      <c r="B535" s="11"/>
+    </row>
+    <row r="536" ht="13.95" spans="2:2">
+      <c r="B536" s="11"/>
+    </row>
+    <row r="537" ht="13.95" spans="2:2">
+      <c r="B537" s="11"/>
+    </row>
+    <row r="538" ht="13.95" spans="2:2">
+      <c r="B538" s="11"/>
+    </row>
+    <row r="539" ht="13.95" spans="2:2">
+      <c r="B539" s="11"/>
+    </row>
+    <row r="540" ht="13.95" spans="2:2">
+      <c r="B540" s="11"/>
+    </row>
+    <row r="541" ht="13.95" spans="2:2">
+      <c r="B541" s="11"/>
+    </row>
+    <row r="542" ht="13.95" spans="2:2">
+      <c r="B542" s="11"/>
+    </row>
+    <row r="543" ht="13.95" spans="2:2">
+      <c r="B543" s="11"/>
+    </row>
+    <row r="544" ht="13.95" spans="2:2">
+      <c r="B544" s="11"/>
+    </row>
+    <row r="545" ht="13.95" spans="2:2">
+      <c r="B545" s="11"/>
+    </row>
+    <row r="546" ht="13.95" spans="2:2">
+      <c r="B546" s="11"/>
+    </row>
+    <row r="547" ht="13.95" spans="2:2">
+      <c r="B547" s="11"/>
+    </row>
+    <row r="548" ht="13.95" spans="2:2">
+      <c r="B548" s="11"/>
+    </row>
+    <row r="549" ht="13.95" spans="2:2">
+      <c r="B549" s="11"/>
+    </row>
+    <row r="550" ht="13.95" spans="2:2">
+      <c r="B550" s="11"/>
+    </row>
+    <row r="551" ht="13.95" spans="2:2">
+      <c r="B551" s="11"/>
+    </row>
+    <row r="552" ht="13.95" spans="2:2">
+      <c r="B552" s="11"/>
+    </row>
+    <row r="553" ht="13.95" spans="2:2">
+      <c r="B553" s="11"/>
+    </row>
+    <row r="554" ht="13.95" spans="2:2">
+      <c r="B554" s="11"/>
+    </row>
+    <row r="555" ht="13.95" spans="2:2">
+      <c r="B555" s="11"/>
+    </row>
+    <row r="556" ht="13.95" spans="2:2">
+      <c r="B556" s="11"/>
+    </row>
+    <row r="557" ht="13.95" spans="2:2">
+      <c r="B557" s="11"/>
+    </row>
+    <row r="558" ht="13.95" spans="2:2">
+      <c r="B558" s="11"/>
+    </row>
+    <row r="559" ht="13.95" spans="2:2">
+      <c r="B559" s="11"/>
+    </row>
+    <row r="560" ht="13.95" spans="2:2">
+      <c r="B560" s="11"/>
+    </row>
+    <row r="561" ht="13.95" spans="2:2">
+      <c r="B561" s="11"/>
+    </row>
+    <row r="562" ht="13.95" spans="2:2">
+      <c r="B562" s="11"/>
+    </row>
+    <row r="563" ht="13.95" spans="2:2">
+      <c r="B563" s="11"/>
+    </row>
+    <row r="564" ht="13.95" spans="2:2">
+      <c r="B564" s="11"/>
+    </row>
+    <row r="565" ht="13.95" spans="2:2">
+      <c r="B565" s="11"/>
+    </row>
+    <row r="566" ht="13.95" spans="2:2">
+      <c r="B566" s="11"/>
+    </row>
+    <row r="567" ht="13.95" spans="2:2">
+      <c r="B567" s="11"/>
+    </row>
+    <row r="568" ht="13.95" spans="2:2">
+      <c r="B568" s="11"/>
+    </row>
+    <row r="569" ht="13.95" spans="2:2">
+      <c r="B569" s="11"/>
+    </row>
+    <row r="570" ht="13.95" spans="2:2">
+      <c r="B570" s="11"/>
+    </row>
+    <row r="571" ht="13.95" spans="2:2">
+      <c r="B571" s="11"/>
+    </row>
+    <row r="572" ht="13.95" spans="2:2">
+      <c r="B572" s="11"/>
+    </row>
+    <row r="573" ht="13.95" spans="2:2">
+      <c r="B573" s="11"/>
+    </row>
+    <row r="574" ht="13.95" spans="2:2">
+      <c r="B574" s="11"/>
+    </row>
+    <row r="575" ht="13.95" spans="2:2">
+      <c r="B575" s="11"/>
+    </row>
+    <row r="576" ht="13.95" spans="2:2">
+      <c r="B576" s="11"/>
+    </row>
+    <row r="577" ht="13.95" spans="2:2">
+      <c r="B577" s="11"/>
+    </row>
+    <row r="578" ht="13.95" spans="2:2">
+      <c r="B578" s="11"/>
+    </row>
+    <row r="579" ht="13.95" spans="2:2">
+      <c r="B579" s="11"/>
+    </row>
+    <row r="580" ht="13.95" spans="2:2">
+      <c r="B580" s="11"/>
+    </row>
+    <row r="581" ht="13.95" spans="2:2">
+      <c r="B581" s="11"/>
+    </row>
+    <row r="582" ht="13.95" spans="2:2">
+      <c r="B582" s="11"/>
+    </row>
+    <row r="583" ht="13.95" spans="2:2">
+      <c r="B583" s="11"/>
+    </row>
+    <row r="584" ht="13.95" spans="2:2">
+      <c r="B584" s="11"/>
+    </row>
+    <row r="585" ht="13.95" spans="2:2">
+      <c r="B585" s="11"/>
+    </row>
+    <row r="586" ht="13.95" spans="2:2">
+      <c r="B586" s="11"/>
+    </row>
+    <row r="587" ht="13.95" spans="2:2">
+      <c r="B587" s="11"/>
+    </row>
+    <row r="588" ht="13.95" spans="2:2">
+      <c r="B588" s="11"/>
+    </row>
+    <row r="589" ht="13.95" spans="2:2">
+      <c r="B589" s="11"/>
+    </row>
+    <row r="590" ht="13.95" spans="2:2">
+      <c r="B590" s="11"/>
+    </row>
+    <row r="591" ht="13.95" spans="2:2">
+      <c r="B591" s="11"/>
+    </row>
+    <row r="592" ht="13.95" spans="2:2">
+      <c r="B592" s="11"/>
+    </row>
+    <row r="593" ht="13.95" spans="2:2">
+      <c r="B593" s="11"/>
+    </row>
+    <row r="594" ht="13.95" spans="2:2">
+      <c r="B594" s="11"/>
+    </row>
+    <row r="595" ht="13.95" spans="2:2">
+      <c r="B595" s="11"/>
+    </row>
+    <row r="596" ht="13.95" spans="2:2">
+      <c r="B596" s="11"/>
+    </row>
+    <row r="597" ht="13.95" spans="2:2">
+      <c r="B597" s="11"/>
+    </row>
+    <row r="598" ht="13.95" spans="2:2">
+      <c r="B598" s="11"/>
+    </row>
+    <row r="599" ht="13.95" spans="2:2">
+      <c r="B599" s="11"/>
+    </row>
+    <row r="600" ht="13.95" spans="2:2">
+      <c r="B600" s="11"/>
+    </row>
+    <row r="601" ht="13.95" spans="2:2">
+      <c r="B601" s="11"/>
+    </row>
+    <row r="602" ht="13.95" spans="2:2">
+      <c r="B602" s="11"/>
+    </row>
+    <row r="603" ht="13.95" spans="2:2">
+      <c r="B603" s="11"/>
+    </row>
+    <row r="604" ht="13.95" spans="2:2">
+      <c r="B604" s="11"/>
+    </row>
+    <row r="605" ht="13.95" spans="2:2">
+      <c r="B605" s="11"/>
+    </row>
+    <row r="606" ht="13.95" spans="2:2">
+      <c r="B606" s="11"/>
+    </row>
+    <row r="607" ht="13.95" spans="2:2">
+      <c r="B607" s="11"/>
+    </row>
+    <row r="608" ht="13.95" spans="2:2">
+      <c r="B608" s="11"/>
+    </row>
+    <row r="609" ht="13.95" spans="2:2">
+      <c r="B609" s="11"/>
+    </row>
+    <row r="610" ht="13.95" spans="2:2">
+      <c r="B610" s="11"/>
+    </row>
+    <row r="611" ht="13.95" spans="2:2">
+      <c r="B611" s="11"/>
+    </row>
+    <row r="612" ht="13.95" spans="2:2">
+      <c r="B612" s="11"/>
+    </row>
+    <row r="613" ht="13.95" spans="2:2">
+      <c r="B613" s="11"/>
+    </row>
+    <row r="614" ht="13.95" spans="2:2">
+      <c r="B614" s="11"/>
+    </row>
+    <row r="615" ht="13.95" spans="2:2">
+      <c r="B615" s="11"/>
+    </row>
+    <row r="616" ht="13.95" spans="2:2">
+      <c r="B616" s="11"/>
+    </row>
+    <row r="617" ht="13.95" spans="2:2">
+      <c r="B617" s="11"/>
+    </row>
+    <row r="618" ht="13.95" spans="2:2">
+      <c r="B618" s="11"/>
+    </row>
+    <row r="619" ht="13.95" spans="2:2">
+      <c r="B619" s="11"/>
+    </row>
+    <row r="620" ht="13.95" spans="2:2">
+      <c r="B620" s="11"/>
+    </row>
+    <row r="621" ht="13.95" spans="2:2">
+      <c r="B621" s="11"/>
+    </row>
+    <row r="622" ht="13.95" spans="2:2">
+      <c r="B622" s="11"/>
+    </row>
+    <row r="623" ht="13.95" spans="2:2">
+      <c r="B623" s="11"/>
+    </row>
+    <row r="624" ht="13.95" spans="2:2">
+      <c r="B624" s="11"/>
+    </row>
+    <row r="625" ht="13.95" spans="2:2">
+      <c r="B625" s="11"/>
+    </row>
+    <row r="626" ht="13.95" spans="2:2">
+      <c r="B626" s="11"/>
+    </row>
+    <row r="627" ht="13.95" spans="2:2">
+      <c r="B627" s="11"/>
+    </row>
+    <row r="628" ht="13.95" spans="2:2">
+      <c r="B628" s="11"/>
+    </row>
+    <row r="629" ht="13.95" spans="2:2">
+      <c r="B629" s="11"/>
+    </row>
+    <row r="630" ht="13.95" spans="2:2">
+      <c r="B630" s="11"/>
+    </row>
+    <row r="631" ht="13.95" spans="2:2">
+      <c r="B631" s="11"/>
+    </row>
+    <row r="632" ht="13.95" spans="2:2">
+      <c r="B632" s="11"/>
+    </row>
+    <row r="633" ht="13.95" spans="2:2">
+      <c r="B633" s="11"/>
+    </row>
+    <row r="634" ht="13.95" spans="2:2">
+      <c r="B634" s="11"/>
+    </row>
+    <row r="635" ht="13.95" spans="2:2">
+      <c r="B635" s="11"/>
+    </row>
+    <row r="636" ht="13.95" spans="2:2">
+      <c r="B636" s="11"/>
+    </row>
+    <row r="637" ht="13.95" spans="2:2">
+      <c r="B637" s="11"/>
+    </row>
+    <row r="638" ht="13.95" spans="2:2">
+      <c r="B638" s="11"/>
+    </row>
+    <row r="639" ht="13.95" spans="2:2">
+      <c r="B639" s="11"/>
+    </row>
+    <row r="640" ht="13.95" spans="2:2">
+      <c r="B640" s="11"/>
+    </row>
+    <row r="641" ht="13.95" spans="2:2">
+      <c r="B641" s="11"/>
+    </row>
+    <row r="642" ht="13.95" spans="2:2">
+      <c r="B642" s="11"/>
+    </row>
+    <row r="643" ht="13.95" spans="2:2">
+      <c r="B643" s="11"/>
+    </row>
+    <row r="644" ht="13.95" spans="2:2">
+      <c r="B644" s="11"/>
+    </row>
+    <row r="645" ht="13.95" spans="2:2">
+      <c r="B645" s="11"/>
+    </row>
+    <row r="646" ht="13.95" spans="2:2">
+      <c r="B646" s="11"/>
+    </row>
+    <row r="647" ht="13.95" spans="2:2">
+      <c r="B647" s="11"/>
+    </row>
+    <row r="648" ht="13.95" spans="2:2">
+      <c r="B648" s="11"/>
+    </row>
+    <row r="649" ht="13.95" spans="2:2">
+      <c r="B649" s="11"/>
+    </row>
+    <row r="650" ht="13.95" spans="2:2">
+      <c r="B650" s="11"/>
+    </row>
+    <row r="651" ht="13.95" spans="2:2">
+      <c r="B651" s="11"/>
+    </row>
+    <row r="652" ht="13.95" spans="2:2">
+      <c r="B652" s="11"/>
+    </row>
+    <row r="653" ht="13.95" spans="2:2">
+      <c r="B653" s="11"/>
+    </row>
+    <row r="654" ht="13.95" spans="2:2">
+      <c r="B654" s="11"/>
+    </row>
+    <row r="655" ht="13.95" spans="2:2">
+      <c r="B655" s="11"/>
+    </row>
+    <row r="656" ht="13.95" spans="2:2">
+      <c r="B656" s="11"/>
+    </row>
+    <row r="657" ht="13.95" spans="2:2">
+      <c r="B657" s="11"/>
+    </row>
+    <row r="658" ht="13.95" spans="2:2">
+      <c r="B658" s="11"/>
+    </row>
+    <row r="659" ht="13.95" spans="2:2">
+      <c r="B659" s="11"/>
+    </row>
+    <row r="660" ht="13.95" spans="2:2">
+      <c r="B660" s="11"/>
+    </row>
+    <row r="661" ht="13.95" spans="2:2">
+      <c r="B661" s="11"/>
+    </row>
+    <row r="662" ht="13.95" spans="2:2">
+      <c r="B662" s="11"/>
+    </row>
+    <row r="663" ht="13.95" spans="2:2">
+      <c r="B663" s="11"/>
+    </row>
+    <row r="664" ht="13.95" spans="2:2">
+      <c r="B664" s="11"/>
+    </row>
+    <row r="665" ht="13.95" spans="2:2">
+      <c r="B665" s="11"/>
+    </row>
+    <row r="666" ht="13.95" spans="2:2">
+      <c r="B666" s="11"/>
+    </row>
+    <row r="667" ht="13.95" spans="2:2">
+      <c r="B667" s="11"/>
+    </row>
+    <row r="668" ht="13.95" spans="2:2">
+      <c r="B668" s="11"/>
+    </row>
+    <row r="669" ht="13.95" spans="2:2">
+      <c r="B669" s="11"/>
+    </row>
+    <row r="670" ht="13.95" spans="2:2">
+      <c r="B670" s="11"/>
+    </row>
+    <row r="671" ht="13.95" spans="2:2">
+      <c r="B671" s="11"/>
+    </row>
+    <row r="672" ht="13.95" spans="2:2">
+      <c r="B672" s="11"/>
+    </row>
+    <row r="673" ht="13.95" spans="2:2">
+      <c r="B673" s="11"/>
+    </row>
+    <row r="674" ht="13.95" spans="2:2">
+      <c r="B674" s="11"/>
+    </row>
+    <row r="675" ht="13.95" spans="2:2">
+      <c r="B675" s="11"/>
+    </row>
+    <row r="676" ht="13.95" spans="2:2">
+      <c r="B676" s="11"/>
+    </row>
+    <row r="677" ht="13.95" spans="2:2">
+      <c r="B677" s="11"/>
+    </row>
+    <row r="678" ht="13.95" spans="2:2">
+      <c r="B678" s="11"/>
+    </row>
+    <row r="679" ht="13.95" spans="2:2">
+      <c r="B679" s="11"/>
+    </row>
+    <row r="680" ht="13.95" spans="2:2">
+      <c r="B680" s="11"/>
+    </row>
+    <row r="681" ht="13.95" spans="2:2">
+      <c r="B681" s="11"/>
+    </row>
+    <row r="682" ht="13.95" spans="2:2">
+      <c r="B682" s="11"/>
+    </row>
+    <row r="683" ht="13.95" spans="2:2">
+      <c r="B683" s="11"/>
+    </row>
+    <row r="684" ht="13.95" spans="2:2">
+      <c r="B684" s="11"/>
+    </row>
+    <row r="685" ht="13.95" spans="2:2">
+      <c r="B685" s="11"/>
+    </row>
+    <row r="686" ht="13.95" spans="2:2">
+      <c r="B686" s="11"/>
+    </row>
+    <row r="687" ht="13.95" spans="2:2">
+      <c r="B687" s="11"/>
+    </row>
+    <row r="688" ht="13.95" spans="2:2">
+      <c r="B688" s="11"/>
+    </row>
+    <row r="689" ht="13.95" spans="2:2">
+      <c r="B689" s="11"/>
+    </row>
+    <row r="690" ht="13.95" spans="2:2">
+      <c r="B690" s="11"/>
+    </row>
+    <row r="691" ht="13.95" spans="2:2">
+      <c r="B691" s="11"/>
+    </row>
+    <row r="692" ht="13.95" spans="2:2">
+      <c r="B692" s="11"/>
+    </row>
+    <row r="693" ht="13.95" spans="2:2">
+      <c r="B693" s="11"/>
+    </row>
+    <row r="694" ht="13.95" spans="2:2">
+      <c r="B694" s="11"/>
+    </row>
+    <row r="695" ht="13.95" spans="2:2">
+      <c r="B695" s="11"/>
+    </row>
+    <row r="696" ht="13.95" spans="2:2">
+      <c r="B696" s="11"/>
+    </row>
+    <row r="697" ht="13.95" spans="2:2">
+      <c r="B697" s="11"/>
+    </row>
+    <row r="698" ht="13.95" spans="2:2">
+      <c r="B698" s="11"/>
+    </row>
+    <row r="699" ht="13.95" spans="2:2">
+      <c r="B699" s="11"/>
+    </row>
+    <row r="700" ht="13.95" spans="2:2">
+      <c r="B700" s="11"/>
+    </row>
+    <row r="701" ht="13.95" spans="2:2">
+      <c r="B701" s="11"/>
+    </row>
+    <row r="702" ht="13.95" spans="2:2">
+      <c r="B702" s="11"/>
+    </row>
+    <row r="703" ht="13.95" spans="2:2">
+      <c r="B703" s="11"/>
+    </row>
+    <row r="704" ht="13.95" spans="2:2">
+      <c r="B704" s="11"/>
+    </row>
+    <row r="705" ht="13.95" spans="2:2">
+      <c r="B705" s="11"/>
+    </row>
+    <row r="706" ht="13.95" spans="2:2">
+      <c r="B706" s="11"/>
+    </row>
+    <row r="707" ht="13.95" spans="2:2">
+      <c r="B707" s="11"/>
+    </row>
+    <row r="708" ht="13.95" spans="2:2">
+      <c r="B708" s="11"/>
+    </row>
+    <row r="709" ht="13.95" spans="2:2">
+      <c r="B709" s="11"/>
+    </row>
+    <row r="710" ht="13.95" spans="2:2">
+      <c r="B710" s="11"/>
+    </row>
+    <row r="711" ht="13.95" spans="2:2">
+      <c r="B711" s="11"/>
+    </row>
+    <row r="712" ht="13.95" spans="2:2">
+      <c r="B712" s="11"/>
+    </row>
+    <row r="713" ht="13.95" spans="2:2">
+      <c r="B713" s="11"/>
+    </row>
+    <row r="714" ht="13.95" spans="2:2">
+      <c r="B714" s="11"/>
+    </row>
+    <row r="715" ht="13.95" spans="2:2">
+      <c r="B715" s="11"/>
+    </row>
+    <row r="716" ht="13.95" spans="2:2">
+      <c r="B716" s="11"/>
+    </row>
+    <row r="717" ht="13.95" spans="2:2">
+      <c r="B717" s="11"/>
+    </row>
+    <row r="718" ht="13.95" spans="2:2">
+      <c r="B718" s="11"/>
+    </row>
+    <row r="719" ht="13.95" spans="2:2">
+      <c r="B719" s="11"/>
+    </row>
+    <row r="720" ht="13.95" spans="2:2">
+      <c r="B720" s="11"/>
+    </row>
+    <row r="721" ht="13.95" spans="2:2">
+      <c r="B721" s="11"/>
+    </row>
+    <row r="722" ht="13.95" spans="2:2">
+      <c r="B722" s="11"/>
+    </row>
+    <row r="723" ht="13.95" spans="2:2">
+      <c r="B723" s="11"/>
+    </row>
+    <row r="724" ht="13.95" spans="2:2">
+      <c r="B724" s="11"/>
+    </row>
+    <row r="725" ht="13.95" spans="2:2">
+      <c r="B725" s="11"/>
+    </row>
+    <row r="726" ht="13.95" spans="2:2">
+      <c r="B726" s="11"/>
+    </row>
+    <row r="727" ht="13.95" spans="2:2">
+      <c r="B727" s="11"/>
+    </row>
+    <row r="728" ht="13.95" spans="2:2">
+      <c r="B728" s="11"/>
+    </row>
+    <row r="729" ht="13.95" spans="2:2">
+      <c r="B729" s="11"/>
+    </row>
+    <row r="730" ht="13.95" spans="2:2">
+      <c r="B730" s="11"/>
+    </row>
+    <row r="731" ht="13.95" spans="2:2">
+      <c r="B731" s="11"/>
+    </row>
+    <row r="732" ht="13.95" spans="2:2">
+      <c r="B732" s="11"/>
+    </row>
+    <row r="733" ht="13.95" spans="2:2">
+      <c r="B733" s="11"/>
+    </row>
+    <row r="734" ht="13.95" spans="2:2">
+      <c r="B734" s="11"/>
+    </row>
+    <row r="735" ht="13.95" spans="2:2">
+      <c r="B735" s="11"/>
+    </row>
+    <row r="736" ht="13.95" spans="2:2">
+      <c r="B736" s="11"/>
+    </row>
+    <row r="737" ht="13.95" spans="2:2">
+      <c r="B737" s="11"/>
+    </row>
+    <row r="738" ht="13.95" spans="2:2">
+      <c r="B738" s="11"/>
+    </row>
+    <row r="739" ht="13.95" spans="2:2">
+      <c r="B739" s="11"/>
+    </row>
+    <row r="740" ht="13.95" spans="2:2">
+      <c r="B740" s="11"/>
+    </row>
+    <row r="741" ht="13.95" spans="2:2">
+      <c r="B741" s="11"/>
+    </row>
+    <row r="742" ht="13.95" spans="2:2">
+      <c r="B742" s="11"/>
+    </row>
+    <row r="743" ht="13.95" spans="2:2">
+      <c r="B743" s="11"/>
+    </row>
+    <row r="744" ht="13.95" spans="2:2">
+      <c r="B744" s="11"/>
+    </row>
+    <row r="745" ht="13.95" spans="2:2">
+      <c r="B745" s="11"/>
+    </row>
+    <row r="746" ht="13.95" spans="2:2">
+      <c r="B746" s="11"/>
+    </row>
+    <row r="747" ht="13.95" spans="2:2">
+      <c r="B747" s="11"/>
+    </row>
+    <row r="748" ht="13.95" spans="2:2">
+      <c r="B748" s="11"/>
+    </row>
+    <row r="749" ht="13.95" spans="2:2">
+      <c r="B749" s="11"/>
+    </row>
+    <row r="750" ht="13.95" spans="2:2">
+      <c r="B750" s="11"/>
+    </row>
+    <row r="751" ht="13.95" spans="2:2">
+      <c r="B751" s="11"/>
+    </row>
+    <row r="752" ht="13.95" spans="2:2">
+      <c r="B752" s="11"/>
+    </row>
+    <row r="753" ht="13.95" spans="2:2">
+      <c r="B753" s="11"/>
+    </row>
+    <row r="754" ht="13.95" spans="2:2">
+      <c r="B754" s="11"/>
+    </row>
+    <row r="755" ht="13.95" spans="2:2">
+      <c r="B755" s="11"/>
+    </row>
+    <row r="756" ht="13.95" spans="2:2">
+      <c r="B756" s="11"/>
+    </row>
+    <row r="757" ht="13.95" spans="2:2">
+      <c r="B757" s="11"/>
+    </row>
+    <row r="758" ht="13.95" spans="2:2">
+      <c r="B758" s="11"/>
+    </row>
+    <row r="759" ht="13.95" spans="2:2">
+      <c r="B759" s="11"/>
+    </row>
+    <row r="760" ht="13.95" spans="2:2">
+      <c r="B760" s="11"/>
+    </row>
+    <row r="761" ht="13.95" spans="2:2">
+      <c r="B761" s="11"/>
+    </row>
+    <row r="762" ht="13.95" spans="2:2">
+      <c r="B762" s="11"/>
+    </row>
+    <row r="763" ht="13.95" spans="2:2">
+      <c r="B763" s="11"/>
+    </row>
+    <row r="764" ht="13.95" spans="2:2">
+      <c r="B764" s="11"/>
+    </row>
+    <row r="765" ht="13.95" spans="2:2">
+      <c r="B765" s="11"/>
+    </row>
+    <row r="766" ht="13.95" spans="2:2">
+      <c r="B766" s="11"/>
+    </row>
+    <row r="767" ht="13.95" spans="2:2">
+      <c r="B767" s="11"/>
+    </row>
+    <row r="768" ht="13.95" spans="2:2">
+      <c r="B768" s="11"/>
+    </row>
+    <row r="769" ht="13.95" spans="2:2">
+      <c r="B769" s="11"/>
+    </row>
+    <row r="770" ht="13.95" spans="2:2">
+      <c r="B770" s="11"/>
+    </row>
+    <row r="771" ht="13.95" spans="2:2">
+      <c r="B771" s="11"/>
+    </row>
+    <row r="772" ht="13.95" spans="2:2">
+      <c r="B772" s="11"/>
+    </row>
+    <row r="773" ht="13.95" spans="2:2">
+      <c r="B773" s="11"/>
+    </row>
+    <row r="774" ht="13.95" spans="2:2">
+      <c r="B774" s="11"/>
+    </row>
+    <row r="775" ht="13.95" spans="2:2">
+      <c r="B775" s="11"/>
+    </row>
+    <row r="776" ht="13.95" spans="2:2">
+      <c r="B776" s="11"/>
+    </row>
+    <row r="777" ht="13.95" spans="2:2">
+      <c r="B777" s="11"/>
+    </row>
+    <row r="778" ht="13.95" spans="2:2">
+      <c r="B778" s="11"/>
+    </row>
+    <row r="779" ht="13.95" spans="2:2">
+      <c r="B779" s="11"/>
+    </row>
+    <row r="780" ht="13.95" spans="2:2">
+      <c r="B780" s="11"/>
+    </row>
+    <row r="781" ht="13.95" spans="2:2">
+      <c r="B781" s="11"/>
+    </row>
+    <row r="782" ht="13.95" spans="2:2">
+      <c r="B782" s="11"/>
+    </row>
+    <row r="783" ht="13.95" spans="2:2">
+      <c r="B783" s="11"/>
+    </row>
+    <row r="784" ht="13.95" spans="2:2">
+      <c r="B784" s="11"/>
+    </row>
+    <row r="785" ht="13.95" spans="2:2">
+      <c r="B785" s="11"/>
+    </row>
+    <row r="786" ht="13.95" spans="2:2">
+      <c r="B786" s="11"/>
+    </row>
+    <row r="787" ht="13.95" spans="2:2">
+      <c r="B787" s="11"/>
+    </row>
+    <row r="788" ht="13.95" spans="2:2">
+      <c r="B788" s="11"/>
+    </row>
+    <row r="789" ht="13.95" spans="2:2">
+      <c r="B789" s="11"/>
+    </row>
+    <row r="790" ht="13.95" spans="2:2">
+      <c r="B790" s="11"/>
+    </row>
+    <row r="791" ht="13.95" spans="2:2">
+      <c r="B791" s="11"/>
+    </row>
+    <row r="792" ht="13.95" spans="2:2">
+      <c r="B792" s="11"/>
+    </row>
+    <row r="793" ht="13.95" spans="2:2">
+      <c r="B793" s="11"/>
+    </row>
+    <row r="794" ht="13.95" spans="2:2">
+      <c r="B794" s="11"/>
+    </row>
+    <row r="795" ht="13.95" spans="2:2">
+      <c r="B795" s="11"/>
+    </row>
+    <row r="796" ht="13.95" spans="2:2">
+      <c r="B796" s="11"/>
+    </row>
+    <row r="797" ht="13.95" spans="2:2">
+      <c r="B797" s="11"/>
+    </row>
+    <row r="798" ht="13.95" spans="2:2">
+      <c r="B798" s="11"/>
+    </row>
+    <row r="799" ht="13.95" spans="2:2">
+      <c r="B799" s="11"/>
+    </row>
+    <row r="800" ht="13.95" spans="2:2">
+      <c r="B800" s="11"/>
+    </row>
+    <row r="801" ht="13.95" spans="2:2">
+      <c r="B801" s="11"/>
+    </row>
+    <row r="802" ht="13.95" spans="2:2">
+      <c r="B802" s="11"/>
+    </row>
+    <row r="803" ht="13.95" spans="2:2">
+      <c r="B803" s="11"/>
+    </row>
+    <row r="804" ht="13.95" spans="2:2">
+      <c r="B804" s="11"/>
+    </row>
+    <row r="805" ht="13.95" spans="2:2">
+      <c r="B805" s="11"/>
+    </row>
+    <row r="806" ht="13.95" spans="2:2">
+      <c r="B806" s="11"/>
+    </row>
+    <row r="807" ht="13.95" spans="2:2">
+      <c r="B807" s="11"/>
+    </row>
+    <row r="808" ht="13.95" spans="2:2">
+      <c r="B808" s="11"/>
+    </row>
+    <row r="809" ht="13.95" spans="2:2">
+      <c r="B809" s="11"/>
+    </row>
+    <row r="810" ht="13.95" spans="2:2">
+      <c r="B810" s="11"/>
+    </row>
+    <row r="811" ht="13.95" spans="2:2">
+      <c r="B811" s="11"/>
+    </row>
+    <row r="812" ht="13.95" spans="2:2">
+      <c r="B812" s="11"/>
+    </row>
+    <row r="813" ht="13.95" spans="2:2">
+      <c r="B813" s="11"/>
+    </row>
+    <row r="814" ht="13.95" spans="2:2">
+      <c r="B814" s="11"/>
+    </row>
+    <row r="815" ht="13.95" spans="2:2">
+      <c r="B815" s="11"/>
+    </row>
+    <row r="816" ht="13.95" spans="2:2">
+      <c r="B816" s="11"/>
+    </row>
+    <row r="817" ht="13.95" spans="2:2">
+      <c r="B817" s="11"/>
+    </row>
+    <row r="818" ht="13.95" spans="2:2">
+      <c r="B818" s="11"/>
+    </row>
+    <row r="819" ht="13.95" spans="2:2">
+      <c r="B819" s="11"/>
+    </row>
+    <row r="820" ht="13.95" spans="2:2">
+      <c r="B820" s="11"/>
+    </row>
+    <row r="821" ht="13.95" spans="2:2">
+      <c r="B821" s="11"/>
+    </row>
+    <row r="822" ht="13.95" spans="2:2">
+      <c r="B822" s="11"/>
+    </row>
+    <row r="823" ht="13.95" spans="2:2">
+      <c r="B823" s="11"/>
+    </row>
+    <row r="824" ht="13.95" spans="2:2">
+      <c r="B824" s="11"/>
+    </row>
+    <row r="825" ht="13.95" spans="2:2">
+      <c r="B825" s="11"/>
+    </row>
+    <row r="826" ht="13.95" spans="2:2">
+      <c r="B826" s="11"/>
+    </row>
+    <row r="827" ht="13.95" spans="2:2">
+      <c r="B827" s="11"/>
+    </row>
+    <row r="828" ht="13.95" spans="2:2">
+      <c r="B828" s="11"/>
+    </row>
+    <row r="829" ht="13.95" spans="2:2">
+      <c r="B829" s="11"/>
+    </row>
+    <row r="830" ht="13.95" spans="2:2">
+      <c r="B830" s="11"/>
+    </row>
+    <row r="831" ht="13.95" spans="2:2">
+      <c r="B831" s="11"/>
+    </row>
+    <row r="832" ht="13.95" spans="2:2">
+      <c r="B832" s="11"/>
+    </row>
+    <row r="833" ht="13.95" spans="2:2">
+      <c r="B833" s="11"/>
+    </row>
+    <row r="834" ht="13.95" spans="2:2">
+      <c r="B834" s="11"/>
+    </row>
+    <row r="835" ht="13.95" spans="2:2">
+      <c r="B835" s="11"/>
+    </row>
+    <row r="836" ht="13.95" spans="2:2">
+      <c r="B836" s="11"/>
+    </row>
+    <row r="837" ht="13.95" spans="2:2">
+      <c r="B837" s="11"/>
+    </row>
+    <row r="838" ht="13.95" spans="2:2">
+      <c r="B838" s="11"/>
+    </row>
+    <row r="839" ht="13.95" spans="2:2">
+      <c r="B839" s="11"/>
+    </row>
+    <row r="840" ht="13.95" spans="2:2">
+      <c r="B840" s="11"/>
+    </row>
+    <row r="841" ht="13.95" spans="2:2">
+      <c r="B841" s="11"/>
+    </row>
+    <row r="842" ht="13.95" spans="2:2">
+      <c r="B842" s="11"/>
+    </row>
+    <row r="843" ht="13.95" spans="2:2">
+      <c r="B843" s="11"/>
+    </row>
+    <row r="844" ht="13.95" spans="2:2">
+      <c r="B844" s="11"/>
+    </row>
+    <row r="845" ht="13.95" spans="2:2">
+      <c r="B845" s="11"/>
+    </row>
+    <row r="846" ht="13.95" spans="2:2">
+      <c r="B846" s="11"/>
+    </row>
+    <row r="847" ht="13.95" spans="2:2">
+      <c r="B847" s="11"/>
+    </row>
+    <row r="848" ht="13.95" spans="2:2">
+      <c r="B848" s="11"/>
+    </row>
+    <row r="849" ht="13.95" spans="2:2">
+      <c r="B849" s="11"/>
+    </row>
+    <row r="850" ht="13.95" spans="2:2">
+      <c r="B850" s="11"/>
+    </row>
+    <row r="851" ht="13.95" spans="2:2">
+      <c r="B851" s="11"/>
+    </row>
+    <row r="852" ht="13.95" spans="2:2">
+      <c r="B852" s="11"/>
+    </row>
+    <row r="853" ht="13.95" spans="2:2">
+      <c r="B853" s="11"/>
+    </row>
+    <row r="854" ht="13.95" spans="2:2">
+      <c r="B854" s="11"/>
+    </row>
+    <row r="855" ht="13.95" spans="2:2">
+      <c r="B855" s="11"/>
+    </row>
+    <row r="856" ht="13.95" spans="2:2">
+      <c r="B856" s="11"/>
+    </row>
+    <row r="857" ht="13.95" spans="2:2">
+      <c r="B857" s="11"/>
+    </row>
+    <row r="858" ht="13.95" spans="2:2">
+      <c r="B858" s="11"/>
+    </row>
+    <row r="859" ht="13.95" spans="2:2">
+      <c r="B859" s="11"/>
+    </row>
+    <row r="860" ht="13.95" spans="2:2">
+      <c r="B860" s="11"/>
+    </row>
+    <row r="861" ht="13.95" spans="2:2">
+      <c r="B861" s="11"/>
+    </row>
+    <row r="862" ht="13.95" spans="2:2">
+      <c r="B862" s="11"/>
+    </row>
+    <row r="863" ht="13.95" spans="2:2">
+      <c r="B863" s="11"/>
+    </row>
+    <row r="864" ht="13.95" spans="2:2">
+      <c r="B864" s="11"/>
+    </row>
+    <row r="865" ht="13.95" spans="2:2">
+      <c r="B865" s="11"/>
+    </row>
+    <row r="866" ht="13.95" spans="2:2">
+      <c r="B866" s="11"/>
+    </row>
+    <row r="867" ht="13.95" spans="2:2">
+      <c r="B867" s="11"/>
+    </row>
+    <row r="868" ht="13.95" spans="2:2">
+      <c r="B868" s="11"/>
+    </row>
+    <row r="869" ht="13.95" spans="2:2">
+      <c r="B869" s="11"/>
+    </row>
+    <row r="870" ht="13.95" spans="2:2">
+      <c r="B870" s="11"/>
+    </row>
+    <row r="871" ht="13.95" spans="2:2">
+      <c r="B871" s="11"/>
+    </row>
+    <row r="872" ht="13.95" spans="2:2">
+      <c r="B872" s="11"/>
+    </row>
+    <row r="873" ht="13.95" spans="2:2">
+      <c r="B873" s="11"/>
+    </row>
+    <row r="874" ht="13.95" spans="2:2">
+      <c r="B874" s="11"/>
+    </row>
+    <row r="875" ht="13.95" spans="2:2">
+      <c r="B875" s="11"/>
+    </row>
+    <row r="876" ht="13.95" spans="2:2">
+      <c r="B876" s="11"/>
+    </row>
+    <row r="877" ht="13.95" spans="2:2">
+      <c r="B877" s="11"/>
+    </row>
+    <row r="878" ht="13.95" spans="2:2">
+      <c r="B878" s="11"/>
+    </row>
+    <row r="879" ht="13.95" spans="2:2">
+      <c r="B879" s="11"/>
+    </row>
+    <row r="880" ht="13.95" spans="2:2">
+      <c r="B880" s="11"/>
+    </row>
+    <row r="881" ht="13.95" spans="2:2">
+      <c r="B881" s="11"/>
+    </row>
+    <row r="882" ht="13.95" spans="2:2">
+      <c r="B882" s="11"/>
+    </row>
+    <row r="883" ht="13.95" spans="2:2">
+      <c r="B883" s="11"/>
+    </row>
+    <row r="884" ht="13.95" spans="2:2">
+      <c r="B884" s="11"/>
+    </row>
+    <row r="885" ht="13.95" spans="2:2">
+      <c r="B885" s="11"/>
+    </row>
+    <row r="886" ht="13.95" spans="2:2">
+      <c r="B886" s="11"/>
+    </row>
+    <row r="887" ht="13.95" spans="2:2">
+      <c r="B887" s="11"/>
+    </row>
+    <row r="888" ht="13.95" spans="2:2">
+      <c r="B888" s="11"/>
+    </row>
+    <row r="889" ht="13.95" spans="2:2">
+      <c r="B889" s="11"/>
+    </row>
+    <row r="890" ht="13.95" spans="2:2">
+      <c r="B890" s="11"/>
+    </row>
+    <row r="891" ht="13.95" spans="2:2">
+      <c r="B891" s="11"/>
+    </row>
+    <row r="892" ht="13.95" spans="2:2">
+      <c r="B892" s="11"/>
+    </row>
+    <row r="893" ht="13.95" spans="2:2">
+      <c r="B893" s="11"/>
+    </row>
+    <row r="894" ht="13.95" spans="2:2">
+      <c r="B894" s="11"/>
+    </row>
+    <row r="895" ht="13.95" spans="2:2">
+      <c r="B895" s="11"/>
+    </row>
+    <row r="896" ht="13.95" spans="2:2">
+      <c r="B896" s="11"/>
+    </row>
+    <row r="897" ht="13.95" spans="2:2">
+      <c r="B897" s="11"/>
+    </row>
+    <row r="898" ht="13.95" spans="2:2">
+      <c r="B898" s="11"/>
+    </row>
+    <row r="899" ht="13.95" spans="2:2">
+      <c r="B899" s="11"/>
+    </row>
+    <row r="900" ht="13.95" spans="2:2">
+      <c r="B900" s="11"/>
+    </row>
+    <row r="901" ht="13.95" spans="2:2">
+      <c r="B901" s="11"/>
+    </row>
+    <row r="902" ht="13.95" spans="2:2">
+      <c r="B902" s="11"/>
+    </row>
+    <row r="903" ht="13.95" spans="2:2">
+      <c r="B903" s="11"/>
+    </row>
+    <row r="904" ht="13.95" spans="2:2">
+      <c r="B904" s="11"/>
+    </row>
+    <row r="905" ht="13.95" spans="2:2">
+      <c r="B905" s="11"/>
+    </row>
+    <row r="906" ht="13.95" spans="2:2">
+      <c r="B906" s="11"/>
+    </row>
+    <row r="907" ht="13.95" spans="2:2">
+      <c r="B907" s="11"/>
+    </row>
+    <row r="908" ht="13.95" spans="2:2">
+      <c r="B908" s="11"/>
+    </row>
+    <row r="909" ht="13.95" spans="2:2">
+      <c r="B909" s="11"/>
+    </row>
+    <row r="910" ht="13.95" spans="2:2">
+      <c r="B910" s="11"/>
+    </row>
+    <row r="911" ht="13.95" spans="2:2">
+      <c r="B911" s="11"/>
+    </row>
+    <row r="912" ht="13.95" spans="2:2">
+      <c r="B912" s="11"/>
+    </row>
+    <row r="913" ht="13.95" spans="2:2">
+      <c r="B913" s="11"/>
+    </row>
+    <row r="914" ht="13.95" spans="2:2">
+      <c r="B914" s="11"/>
+    </row>
+    <row r="915" ht="13.95" spans="2:2">
+      <c r="B915" s="11"/>
+    </row>
+    <row r="916" ht="13.95" spans="2:2">
+      <c r="B916" s="11"/>
+    </row>
+    <row r="917" ht="13.95" spans="2:2">
+      <c r="B917" s="11"/>
+    </row>
+    <row r="918" ht="13.95" spans="2:2">
+      <c r="B918" s="11"/>
+    </row>
+    <row r="919" ht="13.95" spans="2:2">
+      <c r="B919" s="11"/>
+    </row>
+    <row r="920" ht="13.95" spans="2:2">
+      <c r="B920" s="11"/>
+    </row>
+    <row r="921" ht="13.95" spans="2:2">
+      <c r="B921" s="11"/>
+    </row>
+    <row r="922" ht="13.95" spans="2:2">
+      <c r="B922" s="11"/>
+    </row>
+    <row r="923" ht="13.95" spans="2:2">
+      <c r="B923" s="11"/>
+    </row>
+    <row r="924" ht="13.95" spans="2:2">
+      <c r="B924" s="11"/>
+    </row>
+    <row r="925" ht="13.95" spans="2:2">
+      <c r="B925" s="11"/>
+    </row>
+    <row r="926" ht="13.95" spans="2:2">
+      <c r="B926" s="11"/>
+    </row>
+    <row r="927" ht="13.95" spans="2:2">
+      <c r="B927" s="11"/>
+    </row>
+    <row r="928" ht="13.95" spans="2:2">
+      <c r="B928" s="11"/>
+    </row>
+    <row r="929" ht="13.95" spans="2:2">
+      <c r="B929" s="11"/>
+    </row>
+    <row r="930" ht="13.95" spans="2:2">
+      <c r="B930" s="11"/>
+    </row>
+    <row r="931" ht="13.95" spans="2:2">
+      <c r="B931" s="11"/>
+    </row>
+    <row r="932" ht="13.95" spans="2:2">
+      <c r="B932" s="11"/>
+    </row>
+    <row r="933" ht="13.95" spans="2:2">
+      <c r="B933" s="11"/>
+    </row>
+    <row r="934" ht="13.95" spans="2:2">
+      <c r="B934" s="11"/>
+    </row>
+    <row r="935" ht="13.95" spans="2:2">
+      <c r="B935" s="11"/>
+    </row>
+    <row r="936" ht="13.95" spans="2:2">
+      <c r="B936" s="11"/>
+    </row>
+    <row r="937" ht="13.95" spans="2:2">
+      <c r="B937" s="11"/>
+    </row>
+    <row r="938" ht="13.95" spans="2:2">
+      <c r="B938" s="11"/>
+    </row>
+    <row r="939" ht="13.95" spans="2:2">
+      <c r="B939" s="11"/>
+    </row>
+    <row r="940" ht="13.95" spans="2:2">
+      <c r="B940" s="11"/>
+    </row>
+    <row r="941" ht="13.95" spans="2:2">
+      <c r="B941" s="11"/>
+    </row>
+    <row r="942" ht="13.95" spans="2:2">
+      <c r="B942" s="11"/>
+    </row>
+    <row r="943" ht="13.95" spans="2:2">
+      <c r="B943" s="11"/>
+    </row>
+    <row r="944" ht="13.95" spans="2:2">
+      <c r="B944" s="11"/>
+    </row>
+    <row r="945" ht="13.95" spans="2:2">
+      <c r="B945" s="11"/>
+    </row>
+    <row r="946" ht="13.95" spans="2:2">
+      <c r="B946" s="11"/>
+    </row>
+    <row r="947" ht="13.95" spans="2:2">
+      <c r="B947" s="11"/>
+    </row>
+    <row r="948" ht="13.95" spans="2:2">
+      <c r="B948" s="11"/>
+    </row>
+    <row r="949" ht="13.95" spans="2:2">
+      <c r="B949" s="11"/>
+    </row>
+    <row r="950" ht="13.95" spans="2:2">
+      <c r="B950" s="11"/>
+    </row>
+    <row r="951" ht="13.95" spans="2:2">
+      <c r="B951" s="11"/>
+    </row>
+    <row r="952" ht="13.95" spans="2:2">
+      <c r="B952" s="11"/>
+    </row>
+    <row r="953" ht="13.95" spans="2:2">
+      <c r="B953" s="11"/>
+    </row>
+    <row r="954" ht="13.95" spans="2:2">
+      <c r="B954" s="11"/>
+    </row>
+    <row r="955" ht="13.95" spans="2:2">
+      <c r="B955" s="11"/>
+    </row>
+    <row r="956" ht="13.95" spans="2:2">
+      <c r="B956" s="11"/>
+    </row>
+    <row r="957" ht="13.95" spans="2:2">
+      <c r="B957" s="11"/>
+    </row>
+    <row r="958" ht="13.95" spans="2:2">
+      <c r="B958" s="11"/>
+    </row>
+    <row r="959" ht="13.95" spans="2:2">
+      <c r="B959" s="11"/>
+    </row>
+    <row r="960" ht="13.95" spans="2:2">
+      <c r="B960" s="11"/>
+    </row>
+    <row r="961" ht="13.95" spans="2:2">
+      <c r="B961" s="11"/>
+    </row>
+    <row r="962" ht="13.95" spans="2:2">
+      <c r="B962" s="11"/>
+    </row>
+    <row r="963" ht="13.95" spans="2:2">
+      <c r="B963" s="11"/>
+    </row>
+    <row r="964" ht="13.95" spans="2:2">
+      <c r="B964" s="11"/>
+    </row>
+    <row r="965" ht="13.95" spans="2:2">
+      <c r="B965" s="11"/>
+    </row>
+    <row r="966" ht="13.95" spans="2:2">
+      <c r="B966" s="11"/>
+    </row>
+    <row r="967" ht="13.95" spans="2:2">
+      <c r="B967" s="11"/>
+    </row>
+    <row r="968" ht="13.95" spans="2:2">
+      <c r="B968" s="11"/>
+    </row>
+    <row r="969" ht="13.95" spans="2:2">
+      <c r="B969" s="11"/>
+    </row>
+    <row r="970" ht="13.95" spans="2:2">
+      <c r="B970" s="11"/>
+    </row>
+    <row r="971" ht="13.95" spans="2:2">
+      <c r="B971" s="11"/>
+    </row>
+    <row r="972" ht="13.95" spans="2:2">
+      <c r="B972" s="11"/>
+    </row>
+    <row r="973" ht="13.95" spans="2:2">
+      <c r="B973" s="11"/>
+    </row>
+    <row r="974" ht="13.95" spans="2:2">
+      <c r="B974" s="11"/>
+    </row>
+    <row r="975" ht="13.95" spans="2:2">
+      <c r="B975" s="11"/>
+    </row>
+    <row r="976" ht="13.95" spans="2:2">
+      <c r="B976" s="11"/>
+    </row>
+    <row r="977" ht="13.95" spans="2:2">
+      <c r="B977" s="11"/>
+    </row>
+    <row r="978" ht="13.95" spans="2:2">
+      <c r="B978" s="11"/>
+    </row>
+    <row r="979" ht="13.95" spans="2:2">
+      <c r="B979" s="11"/>
+    </row>
+    <row r="980" ht="13.95" spans="2:2">
+      <c r="B980" s="11"/>
+    </row>
+    <row r="981" ht="13.95" spans="2:2">
+      <c r="B981" s="11"/>
+    </row>
+    <row r="982" ht="13.95" spans="2:2">
+      <c r="B982" s="11"/>
+    </row>
+    <row r="983" ht="13.95" spans="2:2">
+      <c r="B983" s="11"/>
+    </row>
+    <row r="984" ht="13.95" spans="2:2">
+      <c r="B984" s="11"/>
+    </row>
+    <row r="985" ht="13.95" spans="2:2">
+      <c r="B985" s="11"/>
+    </row>
+    <row r="986" ht="13.95" spans="2:2">
+      <c r="B986" s="11"/>
+    </row>
+    <row r="987" ht="13.95" spans="2:2">
+      <c r="B987" s="11"/>
+    </row>
+    <row r="988" ht="13.95" spans="2:2">
+      <c r="B988" s="11"/>
+    </row>
+    <row r="989" ht="13.95" spans="2:2">
+      <c r="B989" s="11"/>
+    </row>
+    <row r="990" ht="13.95" spans="2:2">
+      <c r="B990" s="11"/>
+    </row>
+    <row r="991" ht="13.95" spans="2:2">
+      <c r="B991" s="11"/>
+    </row>
+    <row r="992" ht="13.95" spans="2:2">
+      <c r="B992" s="11"/>
+    </row>
+    <row r="993" ht="13.95" spans="2:2">
+      <c r="B993" s="11"/>
+    </row>
+    <row r="994" ht="13.95" spans="2:2">
+      <c r="B994" s="11"/>
+    </row>
+    <row r="995" ht="13.95" spans="2:2">
+      <c r="B995" s="11"/>
+    </row>
+    <row r="996" ht="13.95" spans="2:2">
+      <c r="B996" s="11"/>
+    </row>
+    <row r="997" ht="13.95" spans="2:2">
+      <c r="B997" s="11"/>
+    </row>
+    <row r="998" ht="13.95" spans="2:2">
+      <c r="B998" s="11"/>
+    </row>
+    <row r="999" ht="13.95" spans="2:2">
+      <c r="B999" s="11"/>
+    </row>
+    <row r="1000" ht="13.95" spans="2:2">
+      <c r="B1000" s="11"/>
+    </row>
+  </sheetData>
+  <sortState ref="A2:C130">
+    <sortCondition ref="A2:A130"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>